--- a/data/liste-equipe.xlsx
+++ b/data/liste-equipe.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10609"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10119"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jeremylavalade/Library/CloudStorage/GoogleDrive-b00730264@essec.edu/Drive partagés/L'Harmonie du Doute/3. Services Supports/3. Com' Externe (hors financement)/2. Site Web/2. Site Web/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33B1B887-BE0C-534C-9BB8-24128DA5F04C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAEAA4C4-3379-6847-A896-8837A156C9A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17740" xr2:uid="{786A410D-58C9-CF4E-A296-84671034DD88}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="303">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="456" uniqueCount="355">
   <si>
     <t>Prénom</t>
   </si>
@@ -945,13 +945,169 @@
   </si>
   <si>
     <t>cortadejuliette</t>
+  </si>
+  <si>
+    <t>Poste English</t>
+  </si>
+  <si>
+    <t>Co-Screenwriter</t>
+  </si>
+  <si>
+    <t>Co-Screenwriter &amp; Dialogue Writer</t>
+  </si>
+  <si>
+    <t>Production Manager</t>
+  </si>
+  <si>
+    <t>Production Coordinator</t>
+  </si>
+  <si>
+    <t>1st Assistant Director</t>
+  </si>
+  <si>
+    <t>2nd Assistant Director</t>
+  </si>
+  <si>
+    <t>3rd Assistant Director</t>
+  </si>
+  <si>
+    <t>Script Supervisor</t>
+  </si>
+  <si>
+    <t>Unit Manager</t>
+  </si>
+  <si>
+    <t>Assistant Unit Manager</t>
+  </si>
+  <si>
+    <t>Unit</t>
+  </si>
+  <si>
+    <t>Director of Photography</t>
+  </si>
+  <si>
+    <t>1st Assistant Camera Operator</t>
+  </si>
+  <si>
+    <t>2nd Assistant Camera Operator</t>
+  </si>
+  <si>
+    <t>Gaffer</t>
+  </si>
+  <si>
+    <t>Electrician</t>
+  </si>
+  <si>
+    <t>Key Grip</t>
+  </si>
+  <si>
+    <t>Grip</t>
+  </si>
+  <si>
+    <t>Production Designer - Prep</t>
+  </si>
+  <si>
+    <t>Production Designer - Shoot</t>
+  </si>
+  <si>
+    <t>Construction Manager</t>
+  </si>
+  <si>
+    <t>Set Designer Assistant</t>
+  </si>
+  <si>
+    <t>Graphic Designer</t>
+  </si>
+  <si>
+    <t>Set Decorator</t>
+  </si>
+  <si>
+    <t>Propmaster</t>
+  </si>
+  <si>
+    <t>Sound Recordist</t>
+  </si>
+  <si>
+    <t>Boom Operator</t>
+  </si>
+  <si>
+    <t>Head Costume Designer</t>
+  </si>
+  <si>
+    <t>Assistant Costume Designer</t>
+  </si>
+  <si>
+    <t>Costume Designer</t>
+  </si>
+  <si>
+    <t>Head Makeup Artist</t>
+  </si>
+  <si>
+    <t>Makeup Artist</t>
+  </si>
+  <si>
+    <t>Behind-the-Scenes Director</t>
+  </si>
+  <si>
+    <t>Set Photographer</t>
+  </si>
+  <si>
+    <t>Original Music Composer</t>
+  </si>
+  <si>
+    <t>Casting Director</t>
+  </si>
+  <si>
+    <t>Treasurer of the Association</t>
+  </si>
+  <si>
+    <t>General Secretary of the Association</t>
+  </si>
+  <si>
+    <t>Public Relations Director</t>
+  </si>
+  <si>
+    <t>HR Manager</t>
+  </si>
+  <si>
+    <t>Event Manager</t>
+  </si>
+  <si>
+    <t>Artistic Director</t>
+  </si>
+  <si>
+    <t>Communication Project Manager</t>
+  </si>
+  <si>
+    <t>Financing Project Manager</t>
+  </si>
+  <si>
+    <t>Event Photographer</t>
+  </si>
+  <si>
+    <t>Graphic Design Specialist</t>
+  </si>
+  <si>
+    <t>Sound Mixer</t>
+  </si>
+  <si>
+    <t>VFX Artist</t>
+  </si>
+  <si>
+    <t>Set Design Consultant</t>
+  </si>
+  <si>
+    <t>Extras Coordinator</t>
+  </si>
+  <si>
+    <t>Drone Pilot</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -963,6 +1119,13 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -986,33 +1149,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1342,7 +1490,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6EF1D4DD-F58E-894F-94D4-E9D82FF3EB6B}">
-  <dimension ref="B2:I66"/>
+  <dimension ref="B2:J66"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.33203125" customWidth="1"/>
@@ -1350,12 +1498,13 @@
     <col min="3" max="3" width="10.5" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14.6640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="30.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="23.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="41.33203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="30.33203125" customWidth="1"/>
+    <col min="7" max="7" width="23.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="41.33203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B2" t="s">
         <v>8</v>
       </c>
@@ -1369,16 +1518,19 @@
         <v>13</v>
       </c>
       <c r="F2" t="s">
+        <v>303</v>
+      </c>
+      <c r="G2" t="s">
         <v>2</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>3</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B3" t="s">
         <v>12</v>
       </c>
@@ -1391,14 +1543,17 @@
       <c r="E3" t="s">
         <v>11</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="G3" t="s">
         <v>19</v>
       </c>
-      <c r="G3" t="s">
+      <c r="H3" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B4" t="s">
         <v>12</v>
       </c>
@@ -1411,14 +1566,17 @@
       <c r="E4" t="s">
         <v>16</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F4" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="G4" t="s">
         <v>17</v>
       </c>
-      <c r="G4" t="s">
+      <c r="H4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B5" t="s">
         <v>27</v>
       </c>
@@ -1431,14 +1589,17 @@
       <c r="E5" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="F5" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="G5" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="H5" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B6" t="s">
         <v>27</v>
       </c>
@@ -1451,14 +1612,17 @@
       <c r="E6" t="s">
         <v>24</v>
       </c>
-      <c r="F6" t="s">
+      <c r="F6" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="G6" t="s">
         <v>196</v>
       </c>
-      <c r="G6" t="s">
+      <c r="H6" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B7" t="s">
         <v>27</v>
       </c>
@@ -1471,14 +1635,17 @@
       <c r="E7" t="s">
         <v>24</v>
       </c>
-      <c r="F7" t="s">
+      <c r="F7" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="G7" t="s">
         <v>155</v>
       </c>
-      <c r="G7" t="s">
+      <c r="H7" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B8" t="s">
         <v>28</v>
       </c>
@@ -1491,14 +1658,17 @@
       <c r="E8" t="s">
         <v>206</v>
       </c>
-      <c r="F8" t="s">
+      <c r="F8" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="G8" t="s">
         <v>296</v>
       </c>
-      <c r="G8" t="s">
+      <c r="H8" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B9" t="s">
         <v>28</v>
       </c>
@@ -1511,14 +1681,17 @@
       <c r="E9" t="s">
         <v>209</v>
       </c>
-      <c r="F9" t="s">
+      <c r="F9" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="G9" t="s">
         <v>210</v>
       </c>
-      <c r="G9" t="s">
+      <c r="H9" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B10" t="s">
         <v>28</v>
       </c>
@@ -1531,14 +1704,17 @@
       <c r="E10" t="s">
         <v>214</v>
       </c>
-      <c r="F10" t="s">
+      <c r="F10" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="G10" t="s">
         <v>215</v>
       </c>
-      <c r="G10" t="s">
+      <c r="H10" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B11" t="s">
         <v>28</v>
       </c>
@@ -1551,14 +1727,17 @@
       <c r="E11" t="s">
         <v>33</v>
       </c>
-      <c r="F11" t="s">
+      <c r="F11" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="G11" t="s">
         <v>37</v>
       </c>
-      <c r="G11" t="s">
+      <c r="H11" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="12" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B12" t="s">
         <v>27</v>
       </c>
@@ -1571,14 +1750,17 @@
       <c r="E12" t="s">
         <v>36</v>
       </c>
-      <c r="F12" t="s">
+      <c r="F12" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="G12" t="s">
         <v>39</v>
       </c>
-      <c r="G12" t="s">
+      <c r="H12" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B13" t="s">
         <v>27</v>
       </c>
@@ -1591,14 +1773,17 @@
       <c r="E13" t="s">
         <v>180</v>
       </c>
-      <c r="F13" t="s">
+      <c r="F13" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="G13" t="s">
         <v>161</v>
       </c>
-      <c r="G13" t="s">
+      <c r="H13" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B14" t="s">
         <v>27</v>
       </c>
@@ -1611,14 +1796,17 @@
       <c r="E14" t="s">
         <v>158</v>
       </c>
-      <c r="F14" t="s">
+      <c r="F14" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="G14" t="s">
         <v>219</v>
       </c>
-      <c r="G14" t="s">
+      <c r="H14" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="15" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B15" t="s">
         <v>27</v>
       </c>
@@ -1631,14 +1819,17 @@
       <c r="E15" t="s">
         <v>158</v>
       </c>
-      <c r="F15" t="s">
+      <c r="F15" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="G15" t="s">
         <v>223</v>
       </c>
-      <c r="G15" t="s">
+      <c r="H15" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="16" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="16" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B16" t="s">
         <v>29</v>
       </c>
@@ -1651,14 +1842,17 @@
       <c r="E16" t="s">
         <v>43</v>
       </c>
-      <c r="F16" t="s">
+      <c r="F16" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="G16" t="s">
         <v>44</v>
       </c>
-      <c r="G16" t="s">
+      <c r="H16" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B17" t="s">
         <v>29</v>
       </c>
@@ -1671,14 +1865,17 @@
       <c r="E17" t="s">
         <v>165</v>
       </c>
-      <c r="F17" t="s">
+      <c r="F17" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="G17" t="s">
         <v>166</v>
       </c>
-      <c r="G17" t="s">
+      <c r="H17" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="18" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B18" t="s">
         <v>29</v>
       </c>
@@ -1691,14 +1888,17 @@
       <c r="E18" t="s">
         <v>297</v>
       </c>
-      <c r="F18" t="s">
+      <c r="F18" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="G18" t="s">
         <v>227</v>
       </c>
-      <c r="G18" t="s">
+      <c r="H18" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B19" t="s">
         <v>29</v>
       </c>
@@ -1711,14 +1911,17 @@
       <c r="E19" t="s">
         <v>231</v>
       </c>
-      <c r="F19" t="s">
+      <c r="F19" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="G19" t="s">
         <v>232</v>
       </c>
-      <c r="G19" t="s">
+      <c r="H19" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="20" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B20" t="s">
         <v>29</v>
       </c>
@@ -1731,14 +1934,17 @@
       <c r="E20" t="s">
         <v>235</v>
       </c>
-      <c r="F20" t="s">
+      <c r="F20" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="G20" t="s">
         <v>236</v>
       </c>
-      <c r="G20" t="s">
+      <c r="H20" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="21" spans="2:7" ht="17" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:8" ht="17" x14ac:dyDescent="0.2">
       <c r="B21" t="s">
         <v>29</v>
       </c>
@@ -1751,14 +1957,17 @@
       <c r="E21" t="s">
         <v>235</v>
       </c>
-      <c r="F21" s="2" t="s">
+      <c r="F21" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="G21" s="2" t="s">
         <v>298</v>
       </c>
-      <c r="G21" t="s">
+      <c r="H21" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="22" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B22" t="s">
         <v>29</v>
       </c>
@@ -1771,14 +1980,17 @@
       <c r="E22" t="s">
         <v>242</v>
       </c>
-      <c r="F22" t="s">
+      <c r="F22" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="G22" t="s">
         <v>243</v>
       </c>
-      <c r="G22" t="s">
+      <c r="H22" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="23" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B23" t="s">
         <v>29</v>
       </c>
@@ -1791,14 +2003,17 @@
       <c r="E23" t="s">
         <v>48</v>
       </c>
-      <c r="F23" t="s">
+      <c r="F23" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="G23" t="s">
         <v>54</v>
       </c>
-      <c r="G23" t="s">
+      <c r="H23" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="24" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B24" t="s">
         <v>29</v>
       </c>
@@ -1811,14 +2026,17 @@
       <c r="E24" t="s">
         <v>48</v>
       </c>
-      <c r="F24" t="s">
+      <c r="F24" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="G24" t="s">
         <v>56</v>
       </c>
-      <c r="G24" t="s">
+      <c r="H24" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="25" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B25" t="s">
         <v>28</v>
       </c>
@@ -1831,14 +2049,17 @@
       <c r="E25" t="s">
         <v>53</v>
       </c>
-      <c r="F25" t="s">
+      <c r="F25" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="G25" t="s">
         <v>58</v>
       </c>
-      <c r="G25" t="s">
+      <c r="H25" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="26" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B26" t="s">
         <v>28</v>
       </c>
@@ -1851,14 +2072,17 @@
       <c r="E26" t="s">
         <v>169</v>
       </c>
-      <c r="F26" t="s">
+      <c r="F26" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="G26" t="s">
         <v>170</v>
       </c>
-      <c r="G26" t="s">
+      <c r="H26" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="27" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B27" t="s">
         <v>28</v>
       </c>
@@ -1871,14 +2095,17 @@
       <c r="E27" t="s">
         <v>61</v>
       </c>
-      <c r="F27" t="s">
+      <c r="F27" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="G27" t="s">
         <v>7</v>
       </c>
-      <c r="G27" t="s">
+      <c r="H27" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="28" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B28" t="s">
         <v>28</v>
       </c>
@@ -1891,14 +2118,17 @@
       <c r="E28" t="s">
         <v>247</v>
       </c>
-      <c r="F28" t="s">
+      <c r="F28" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="G28" t="s">
         <v>248</v>
       </c>
-      <c r="G28" t="s">
+      <c r="H28" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="29" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="29" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B29" t="s">
         <v>28</v>
       </c>
@@ -1911,14 +2141,17 @@
       <c r="E29" t="s">
         <v>247</v>
       </c>
-      <c r="F29" t="s">
+      <c r="F29" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="G29" t="s">
         <v>251</v>
       </c>
-      <c r="G29" t="s">
+      <c r="H29" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="30" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="30" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B30" t="s">
         <v>28</v>
       </c>
@@ -1931,14 +2164,17 @@
       <c r="E30" t="s">
         <v>255</v>
       </c>
-      <c r="F30" t="s">
+      <c r="F30" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="G30" t="s">
         <v>256</v>
       </c>
-      <c r="G30" t="s">
+      <c r="H30" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="31" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="31" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B31" t="s">
         <v>28</v>
       </c>
@@ -1951,14 +2187,17 @@
       <c r="E31" t="s">
         <v>247</v>
       </c>
-      <c r="F31" t="s">
+      <c r="F31" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="G31" t="s">
         <v>260</v>
       </c>
-      <c r="G31" t="s">
+      <c r="H31" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="32" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="32" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B32" t="s">
         <v>28</v>
       </c>
@@ -1971,14 +2210,17 @@
       <c r="E32" t="s">
         <v>255</v>
       </c>
-      <c r="F32" t="s">
+      <c r="F32" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="G32" t="s">
         <v>264</v>
       </c>
-      <c r="G32" t="s">
+      <c r="H32" t="s">
         <v>265</v>
       </c>
     </row>
-    <row r="33" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B33" t="s">
         <v>28</v>
       </c>
@@ -1991,14 +2233,17 @@
       <c r="E33" t="s">
         <v>268</v>
       </c>
-      <c r="F33" t="s">
+      <c r="F33" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="G33" t="s">
         <v>269</v>
       </c>
-      <c r="G33" t="s">
+      <c r="H33" t="s">
         <v>270</v>
       </c>
     </row>
-    <row r="34" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B34" t="s">
         <v>28</v>
       </c>
@@ -2011,14 +2256,17 @@
       <c r="E34" t="s">
         <v>273</v>
       </c>
-      <c r="F34" t="s">
+      <c r="F34" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="G34" t="s">
         <v>274</v>
       </c>
-      <c r="G34" t="s">
+      <c r="H34" t="s">
         <v>275</v>
       </c>
     </row>
-    <row r="35" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B35" t="s">
         <v>28</v>
       </c>
@@ -2031,14 +2279,17 @@
       <c r="E35" t="s">
         <v>64</v>
       </c>
-      <c r="F35" t="s">
+      <c r="F35" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="G35" t="s">
         <v>65</v>
       </c>
-      <c r="G35" t="s">
+      <c r="H35" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="36" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="36" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B36" t="s">
         <v>29</v>
       </c>
@@ -2051,14 +2302,17 @@
       <c r="E36" t="s">
         <v>179</v>
       </c>
-      <c r="F36" t="s">
+      <c r="F36" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="G36" t="s">
         <v>77</v>
       </c>
-      <c r="G36" t="s">
+      <c r="H36" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="37" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B37" t="s">
         <v>29</v>
       </c>
@@ -2071,14 +2325,17 @@
       <c r="E37" t="s">
         <v>70</v>
       </c>
-      <c r="F37" t="s">
+      <c r="F37" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="G37" t="s">
         <v>79</v>
       </c>
-      <c r="G37" t="s">
+      <c r="H37" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="38" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B38" t="s">
         <v>28</v>
       </c>
@@ -2091,14 +2348,17 @@
       <c r="E38" t="s">
         <v>73</v>
       </c>
-      <c r="F38" t="s">
+      <c r="F38" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="G38" t="s">
         <v>81</v>
       </c>
-      <c r="G38" t="s">
+      <c r="H38" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="39" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B39" t="s">
         <v>28</v>
       </c>
@@ -2111,14 +2371,17 @@
       <c r="E39" t="s">
         <v>76</v>
       </c>
-      <c r="F39" t="s">
+      <c r="F39" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="G39" t="s">
         <v>83</v>
       </c>
-      <c r="G39" t="s">
+      <c r="H39" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="40" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B40" t="s">
         <v>28</v>
       </c>
@@ -2131,14 +2394,17 @@
       <c r="E40" t="s">
         <v>300</v>
       </c>
-      <c r="F40" t="s">
+      <c r="F40" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="G40" t="s">
         <v>87</v>
       </c>
-      <c r="G40" t="s">
+      <c r="H40" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="41" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B41" t="s">
         <v>28</v>
       </c>
@@ -2151,14 +2417,17 @@
       <c r="E41" t="s">
         <v>300</v>
       </c>
-      <c r="F41" t="s">
+      <c r="F41" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="G41" t="s">
         <v>301</v>
       </c>
-      <c r="G41" t="s">
+      <c r="H41" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="42" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B42" t="s">
         <v>29</v>
       </c>
@@ -2171,14 +2440,17 @@
       <c r="E42" t="s">
         <v>281</v>
       </c>
-      <c r="F42" t="s">
+      <c r="F42" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="G42" t="s">
         <v>282</v>
       </c>
-      <c r="G42" t="s">
+      <c r="H42" t="s">
         <v>283</v>
       </c>
     </row>
-    <row r="43" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B43" t="s">
         <v>29</v>
       </c>
@@ -2191,14 +2463,17 @@
       <c r="E43" t="s">
         <v>286</v>
       </c>
-      <c r="F43" t="s">
+      <c r="F43" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="G43" t="s">
         <v>287</v>
       </c>
-      <c r="G43" t="s">
+      <c r="H43" t="s">
         <v>288</v>
       </c>
     </row>
-    <row r="44" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B44" t="s">
         <v>28</v>
       </c>
@@ -2211,14 +2486,17 @@
       <c r="E44" t="s">
         <v>174</v>
       </c>
-      <c r="F44" t="s">
+      <c r="F44" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="G44" t="s">
         <v>175</v>
       </c>
-      <c r="G44" t="s">
+      <c r="H44" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="45" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B45" t="s">
         <v>28</v>
       </c>
@@ -2231,14 +2509,17 @@
       <c r="E45" t="s">
         <v>290</v>
       </c>
-      <c r="F45" t="s">
+      <c r="F45" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="G45" t="s">
         <v>302</v>
       </c>
-      <c r="G45" t="s">
+      <c r="H45" t="s">
         <v>291</v>
       </c>
     </row>
-    <row r="46" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B46" t="s">
         <v>28</v>
       </c>
@@ -2251,14 +2532,17 @@
       <c r="E46" t="s">
         <v>91</v>
       </c>
-      <c r="F46" t="s">
+      <c r="F46" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="G46" t="s">
         <v>92</v>
       </c>
-      <c r="G46" t="s">
+      <c r="H46" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="47" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B47" t="s">
         <v>145</v>
       </c>
@@ -2271,14 +2555,17 @@
       <c r="E47" t="s">
         <v>147</v>
       </c>
-      <c r="F47" t="s">
+      <c r="F47" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="G47" t="s">
         <v>182</v>
       </c>
-      <c r="G47" t="s">
+      <c r="H47" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="48" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B48" t="s">
         <v>145</v>
       </c>
@@ -2291,14 +2578,17 @@
       <c r="E48" t="s">
         <v>147</v>
       </c>
-      <c r="F48" t="s">
+      <c r="F48" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="G48" t="s">
         <v>65</v>
       </c>
-      <c r="G48" t="s">
+      <c r="H48" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="49" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="49" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B49" t="s">
         <v>30</v>
       </c>
@@ -2311,14 +2601,17 @@
       <c r="E49" t="s">
         <v>110</v>
       </c>
-      <c r="F49" t="s">
+      <c r="F49" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="G49" t="s">
         <v>133</v>
       </c>
-      <c r="G49" t="s">
+      <c r="H49" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="50" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="50" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B50" t="s">
         <v>30</v>
       </c>
@@ -2331,14 +2624,17 @@
       <c r="E50" t="s">
         <v>99</v>
       </c>
-      <c r="F50" t="s">
+      <c r="F50" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="G50" t="s">
         <v>125</v>
       </c>
-      <c r="G50" t="s">
+      <c r="H50" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="51" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="51" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B51" t="s">
         <v>30</v>
       </c>
@@ -2351,14 +2647,17 @@
       <c r="E51" t="s">
         <v>205</v>
       </c>
-      <c r="F51" t="s">
+      <c r="F51" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="G51" t="s">
         <v>5</v>
       </c>
-      <c r="G51" t="s">
+      <c r="H51" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="52" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="52" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B52" t="s">
         <v>30</v>
       </c>
@@ -2371,14 +2670,17 @@
       <c r="E52" t="s">
         <v>102</v>
       </c>
-      <c r="F52" t="s">
+      <c r="F52" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="G52" t="s">
         <v>127</v>
       </c>
-      <c r="G52" t="s">
+      <c r="H52" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="53" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="53" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B53" t="s">
         <v>30</v>
       </c>
@@ -2391,14 +2693,17 @@
       <c r="E53" t="s">
         <v>105</v>
       </c>
-      <c r="F53" t="s">
+      <c r="F53" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="G53" t="s">
         <v>129</v>
       </c>
-      <c r="G53" t="s">
+      <c r="H53" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="54" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="54" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B54" t="s">
         <v>30</v>
       </c>
@@ -2411,14 +2716,17 @@
       <c r="E54" t="s">
         <v>108</v>
       </c>
-      <c r="F54" t="s">
+      <c r="F54" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="G54" t="s">
         <v>131</v>
       </c>
-      <c r="G54" t="s">
+      <c r="H54" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="55" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="55" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B55" t="s">
         <v>30</v>
       </c>
@@ -2431,14 +2739,17 @@
       <c r="E55" t="s">
         <v>113</v>
       </c>
-      <c r="F55" t="s">
+      <c r="F55" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="G55" t="s">
         <v>135</v>
       </c>
-      <c r="G55" t="s">
+      <c r="H55" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="56" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="56" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B56" t="s">
         <v>30</v>
       </c>
@@ -2451,14 +2762,17 @@
       <c r="E56" t="s">
         <v>116</v>
       </c>
-      <c r="F56" t="s">
+      <c r="F56" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="G56" t="s">
         <v>137</v>
       </c>
-      <c r="G56" t="s">
+      <c r="H56" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="57" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="57" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B57" t="s">
         <v>30</v>
       </c>
@@ -2471,14 +2785,17 @@
       <c r="E57" t="s">
         <v>119</v>
       </c>
-      <c r="F57" t="s">
+      <c r="F57" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="G57" t="s">
         <v>139</v>
       </c>
-      <c r="G57" t="s">
+      <c r="H57" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="58" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="58" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B58" t="s">
         <v>30</v>
       </c>
@@ -2491,14 +2808,17 @@
       <c r="E58" t="s">
         <v>119</v>
       </c>
-      <c r="F58" t="s">
+      <c r="F58" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="G58" t="s">
         <v>141</v>
       </c>
-      <c r="G58" t="s">
+      <c r="H58" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="59" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="59" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B59" t="s">
         <v>30</v>
       </c>
@@ -2511,14 +2831,17 @@
       <c r="E59" t="s">
         <v>124</v>
       </c>
-      <c r="F59" t="s">
+      <c r="F59" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="G59" t="s">
         <v>143</v>
       </c>
-      <c r="G59" t="s">
+      <c r="H59" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="60" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="60" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B60" t="s">
         <v>30</v>
       </c>
@@ -2531,14 +2854,17 @@
       <c r="E60" t="s">
         <v>150</v>
       </c>
-      <c r="F60" t="s">
+      <c r="F60" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="G60" t="s">
         <v>151</v>
       </c>
-      <c r="G60" t="s">
+      <c r="H60" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="61" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="61" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B61" t="s">
         <v>177</v>
       </c>
@@ -2551,14 +2877,17 @@
       <c r="E61" t="s">
         <v>178</v>
       </c>
-      <c r="F61" t="s">
+      <c r="F61" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="G61" t="s">
         <v>77</v>
       </c>
-      <c r="G61" t="s">
+      <c r="H61" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="62" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="62" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B62" t="s">
         <v>177</v>
       </c>
@@ -2571,14 +2900,17 @@
       <c r="E62" t="s">
         <v>294</v>
       </c>
-      <c r="F62" t="s">
+      <c r="F62" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="G62" t="s">
         <v>296</v>
       </c>
-      <c r="G62" t="s">
+      <c r="H62" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="63" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="63" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B63" t="s">
         <v>185</v>
       </c>
@@ -2591,14 +2923,17 @@
       <c r="E63" t="s">
         <v>188</v>
       </c>
-      <c r="F63" t="s">
+      <c r="F63" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="G63" t="s">
         <v>194</v>
       </c>
-      <c r="G63" t="s">
+      <c r="H63" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="64" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="64" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B64" t="s">
         <v>185</v>
       </c>
@@ -2611,14 +2946,17 @@
       <c r="E64" t="s">
         <v>191</v>
       </c>
-      <c r="F64" t="s">
+      <c r="F64" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="G64" t="s">
         <v>195</v>
       </c>
-      <c r="G64" t="s">
+      <c r="H64" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="65" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B65" t="s">
         <v>185</v>
       </c>
@@ -2631,14 +2969,17 @@
       <c r="E65" t="s">
         <v>199</v>
       </c>
-      <c r="F65" t="s">
+      <c r="F65" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="G65" t="s">
         <v>202</v>
       </c>
-      <c r="G65" t="s">
+      <c r="H65" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="66" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B66" t="s">
         <v>185</v>
       </c>
@@ -2651,10 +2992,13 @@
       <c r="E66" t="s">
         <v>201</v>
       </c>
-      <c r="F66" t="s">
+      <c r="F66" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="G66" t="s">
         <v>203</v>
       </c>
-      <c r="G66" t="s">
+      <c r="H66" t="s">
         <v>204</v>
       </c>
     </row>

--- a/data/liste-equipe.xlsx
+++ b/data/liste-equipe.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jeremylavalade/Library/CloudStorage/GoogleDrive-b00730264@essec.edu/Drive partagés/L'Harmonie du Doute/3. Services Supports/3. Com' Externe (hors financement)/2. Site Web/2. Site Web/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAEAA4C4-3379-6847-A896-8837A156C9A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED4395DB-91DE-424B-8B07-CC792D6B448A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17740" xr2:uid="{786A410D-58C9-CF4E-A296-84671034DD88}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="456" uniqueCount="355">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="498" uniqueCount="365">
   <si>
     <t>Prénom</t>
   </si>
@@ -155,12 +155,6 @@
     <t>philippine.schmitt@harmoniedudoutefilm.fr</t>
   </si>
   <si>
-    <t>flav_ience</t>
-  </si>
-  <si>
-    <t>flavien.hacques@harmoniedudoutefilm.fr</t>
-  </si>
-  <si>
     <t>Romain</t>
   </si>
   <si>
@@ -305,21 +299,9 @@
     <t>maelle.leroux@harmoniedudoutefilm.fr</t>
   </si>
   <si>
-    <t>Nathanaël</t>
-  </si>
-  <si>
-    <t>Sohm</t>
-  </si>
-  <si>
     <t>Compositeur Bande Originale</t>
   </si>
   <si>
-    <t>nathanaelsh_</t>
-  </si>
-  <si>
-    <t>nathanael.sohm@harmoniedudoutefilm.fr</t>
-  </si>
-  <si>
     <t>Martine</t>
   </si>
   <si>
@@ -521,12 +503,6 @@
     <t>Genamez</t>
   </si>
   <si>
-    <t>cecetook</t>
-  </si>
-  <si>
-    <t>cece.genamez@harmoniedudoutefilm.fr</t>
-  </si>
-  <si>
     <t>Mathias</t>
   </si>
   <si>
@@ -695,24 +671,12 @@
     <t>D'Agostino</t>
   </si>
   <si>
-    <t>chaa__chooo</t>
-  </si>
-  <si>
-    <t>charlotte.d'agostino@harmoniedudoutefilm.fr</t>
-  </si>
-  <si>
     <t>Inès</t>
   </si>
   <si>
     <t>Morillon</t>
   </si>
   <si>
-    <t>dermindspi</t>
-  </si>
-  <si>
-    <t>ines.morillon@harmoniedudoutefilm.fr</t>
-  </si>
-  <si>
     <t>Frida</t>
   </si>
   <si>
@@ -725,9 +689,6 @@
     <t>frida.cota@harmoniedudoutefilm.fr</t>
   </si>
   <si>
-    <t>Aloîs</t>
-  </si>
-  <si>
     <t>Melon</t>
   </si>
   <si>
@@ -914,18 +875,9 @@
     <t>juliette.cortade@harmoniedudoutefilm.fr</t>
   </si>
   <si>
-    <t>Pierlou</t>
-  </si>
-  <si>
-    <t>Boudet</t>
-  </si>
-  <si>
     <t>Artiste VFX</t>
   </si>
   <si>
-    <t>pierlou.boudet@harmoniedudoutefilm.fr</t>
-  </si>
-  <si>
     <t>harmoniedudoutefilm</t>
   </si>
   <si>
@@ -1052,9 +1004,6 @@
     <t>Set Photographer</t>
   </si>
   <si>
-    <t>Original Music Composer</t>
-  </si>
-  <si>
     <t>Casting Director</t>
   </si>
   <si>
@@ -1101,6 +1050,87 @@
   </si>
   <si>
     <t>Drone Pilot</t>
+  </si>
+  <si>
+    <t>Aurélien</t>
+  </si>
+  <si>
+    <t>Scelles</t>
+  </si>
+  <si>
+    <t>aurelien.scelles@harmoniedudoutefilm.fr</t>
+  </si>
+  <si>
+    <t>Hugo</t>
+  </si>
+  <si>
+    <t>Loureiro</t>
+  </si>
+  <si>
+    <t>Guillaume</t>
+  </si>
+  <si>
+    <t>Loreau</t>
+  </si>
+  <si>
+    <t>Aloïs</t>
+  </si>
+  <si>
+    <t>Léonce</t>
+  </si>
+  <si>
+    <t>Langlois Favier</t>
+  </si>
+  <si>
+    <t>leonce.langlois-favier@harmoniedudoutefilm.fr</t>
+  </si>
+  <si>
+    <t>Lisa</t>
+  </si>
+  <si>
+    <t>Designeuse Affiche</t>
+  </si>
+  <si>
+    <t>lisa_allouche</t>
+  </si>
+  <si>
+    <t>Poster Graphic Designer</t>
+  </si>
+  <si>
+    <t>Monteur</t>
+  </si>
+  <si>
+    <t>Film Composer</t>
+  </si>
+  <si>
+    <t>Editor</t>
+  </si>
+  <si>
+    <t>lisa.allouche@harmoniedudoutefilm.fr</t>
+  </si>
+  <si>
+    <t>Colorist</t>
+  </si>
+  <si>
+    <t>Etalonneur</t>
+  </si>
+  <si>
+    <t>Chléa</t>
+  </si>
+  <si>
+    <t>Jonard</t>
+  </si>
+  <si>
+    <t>Renfort Maquillage</t>
+  </si>
+  <si>
+    <t>Extra Makeup Artist</t>
+  </si>
+  <si>
+    <t>chlea.mua</t>
+  </si>
+  <si>
+    <t>umbrella_visual</t>
   </si>
 </sst>
 </file>
@@ -1490,7 +1520,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6EF1D4DD-F58E-894F-94D4-E9D82FF3EB6B}">
-  <dimension ref="B2:J66"/>
+  <dimension ref="B2:J72"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.33203125" customWidth="1"/>
@@ -1518,7 +1548,7 @@
         <v>13</v>
       </c>
       <c r="F2" t="s">
-        <v>303</v>
+        <v>287</v>
       </c>
       <c r="G2" t="s">
         <v>2</v>
@@ -1527,7 +1557,7 @@
         <v>3</v>
       </c>
       <c r="J2" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
     </row>
     <row r="3" spans="2:10" x14ac:dyDescent="0.2">
@@ -1544,7 +1574,7 @@
         <v>11</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>304</v>
+        <v>288</v>
       </c>
       <c r="G3" t="s">
         <v>19</v>
@@ -1567,7 +1597,7 @@
         <v>16</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>305</v>
+        <v>289</v>
       </c>
       <c r="G4" t="s">
         <v>17</v>
@@ -1590,7 +1620,7 @@
         <v>23</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>306</v>
+        <v>290</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>25</v>
@@ -1604,22 +1634,22 @@
         <v>27</v>
       </c>
       <c r="C6" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="D6" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="E6" t="s">
         <v>24</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>307</v>
+        <v>291</v>
       </c>
       <c r="G6" t="s">
+        <v>188</v>
+      </c>
+      <c r="H6" t="s">
         <v>196</v>
-      </c>
-      <c r="H6" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="7" spans="2:10" x14ac:dyDescent="0.2">
@@ -1627,22 +1657,22 @@
         <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="D7" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="E7" t="s">
         <v>24</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>307</v>
+        <v>291</v>
       </c>
       <c r="G7" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="H7" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
     </row>
     <row r="8" spans="2:10" x14ac:dyDescent="0.2">
@@ -1650,22 +1680,22 @@
         <v>28</v>
       </c>
       <c r="C8" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D8" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="E8" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>308</v>
+        <v>292</v>
       </c>
       <c r="G8" t="s">
-        <v>296</v>
+        <v>280</v>
       </c>
       <c r="H8" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.2">
@@ -1673,22 +1703,22 @@
         <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="D9" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="E9" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>309</v>
+        <v>293</v>
       </c>
       <c r="G9" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="H9" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.2">
@@ -1696,22 +1726,22 @@
         <v>28</v>
       </c>
       <c r="C10" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="D10" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="E10" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>310</v>
+        <v>294</v>
       </c>
       <c r="G10" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="H10" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
     </row>
     <row r="11" spans="2:10" x14ac:dyDescent="0.2">
@@ -1728,7 +1758,7 @@
         <v>33</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>311</v>
+        <v>295</v>
       </c>
       <c r="G11" t="s">
         <v>37</v>
@@ -1751,13 +1781,13 @@
         <v>36</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>312</v>
+        <v>296</v>
       </c>
       <c r="G12" t="s">
-        <v>39</v>
+        <v>280</v>
       </c>
       <c r="H12" t="s">
-        <v>40</v>
+        <v>196</v>
       </c>
     </row>
     <row r="13" spans="2:10" x14ac:dyDescent="0.2">
@@ -1765,22 +1795,22 @@
         <v>27</v>
       </c>
       <c r="C13" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="D13" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="E13" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>313</v>
+        <v>297</v>
       </c>
       <c r="G13" t="s">
-        <v>161</v>
+        <v>280</v>
       </c>
       <c r="H13" t="s">
-        <v>162</v>
+        <v>196</v>
       </c>
     </row>
     <row r="14" spans="2:10" x14ac:dyDescent="0.2">
@@ -1788,22 +1818,22 @@
         <v>27</v>
       </c>
       <c r="C14" t="s">
-        <v>217</v>
+        <v>341</v>
       </c>
       <c r="D14" t="s">
-        <v>218</v>
+        <v>342</v>
       </c>
       <c r="E14" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>314</v>
+        <v>298</v>
       </c>
       <c r="G14" t="s">
-        <v>219</v>
+        <v>280</v>
       </c>
       <c r="H14" t="s">
-        <v>220</v>
+        <v>196</v>
       </c>
     </row>
     <row r="15" spans="2:10" x14ac:dyDescent="0.2">
@@ -1811,68 +1841,68 @@
         <v>27</v>
       </c>
       <c r="C15" t="s">
-        <v>221</v>
+        <v>343</v>
       </c>
       <c r="D15" t="s">
-        <v>222</v>
+        <v>344</v>
       </c>
       <c r="E15" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>314</v>
+        <v>298</v>
       </c>
       <c r="G15" t="s">
-        <v>223</v>
+        <v>280</v>
       </c>
       <c r="H15" t="s">
-        <v>224</v>
+        <v>196</v>
       </c>
     </row>
     <row r="16" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B16" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C16" t="s">
-        <v>41</v>
+        <v>209</v>
       </c>
       <c r="D16" t="s">
-        <v>42</v>
+        <v>210</v>
       </c>
       <c r="E16" t="s">
-        <v>43</v>
+        <v>152</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>315</v>
+        <v>298</v>
       </c>
       <c r="G16" t="s">
-        <v>44</v>
+        <v>280</v>
       </c>
       <c r="H16" t="s">
-        <v>45</v>
+        <v>196</v>
       </c>
     </row>
     <row r="17" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B17" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C17" t="s">
-        <v>163</v>
+        <v>211</v>
       </c>
       <c r="D17" t="s">
-        <v>164</v>
+        <v>212</v>
       </c>
       <c r="E17" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>316</v>
+        <v>298</v>
       </c>
       <c r="G17" t="s">
-        <v>166</v>
+        <v>280</v>
       </c>
       <c r="H17" t="s">
-        <v>167</v>
+        <v>196</v>
       </c>
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.2">
@@ -1880,22 +1910,22 @@
         <v>29</v>
       </c>
       <c r="C18" t="s">
-        <v>225</v>
+        <v>39</v>
       </c>
       <c r="D18" t="s">
-        <v>226</v>
+        <v>40</v>
       </c>
       <c r="E18" t="s">
-        <v>297</v>
+        <v>41</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>317</v>
+        <v>299</v>
       </c>
       <c r="G18" t="s">
-        <v>227</v>
+        <v>42</v>
       </c>
       <c r="H18" t="s">
-        <v>228</v>
+        <v>43</v>
       </c>
     </row>
     <row r="19" spans="2:8" x14ac:dyDescent="0.2">
@@ -1903,22 +1933,22 @@
         <v>29</v>
       </c>
       <c r="C19" t="s">
-        <v>229</v>
+        <v>155</v>
       </c>
       <c r="D19" t="s">
-        <v>230</v>
+        <v>156</v>
       </c>
       <c r="E19" t="s">
-        <v>231</v>
+        <v>157</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>318</v>
+        <v>300</v>
       </c>
       <c r="G19" t="s">
-        <v>232</v>
+        <v>158</v>
       </c>
       <c r="H19" t="s">
-        <v>299</v>
+        <v>159</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.2">
@@ -1926,45 +1956,45 @@
         <v>29</v>
       </c>
       <c r="C20" t="s">
-        <v>233</v>
+        <v>213</v>
       </c>
       <c r="D20" t="s">
-        <v>234</v>
+        <v>214</v>
       </c>
       <c r="E20" t="s">
-        <v>235</v>
+        <v>281</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>319</v>
+        <v>301</v>
       </c>
       <c r="G20" t="s">
-        <v>236</v>
+        <v>215</v>
       </c>
       <c r="H20" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="21" spans="2:8" ht="17" x14ac:dyDescent="0.2">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="21" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B21" t="s">
         <v>29</v>
       </c>
       <c r="C21" t="s">
-        <v>238</v>
+        <v>345</v>
       </c>
       <c r="D21" t="s">
-        <v>239</v>
+        <v>217</v>
       </c>
       <c r="E21" t="s">
-        <v>235</v>
+        <v>218</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>319</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>298</v>
+        <v>302</v>
+      </c>
+      <c r="G21" t="s">
+        <v>219</v>
       </c>
       <c r="H21" t="s">
-        <v>240</v>
+        <v>283</v>
       </c>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.2">
@@ -1972,45 +2002,45 @@
         <v>29</v>
       </c>
       <c r="C22" t="s">
-        <v>208</v>
+        <v>220</v>
       </c>
       <c r="D22" t="s">
-        <v>241</v>
+        <v>221</v>
       </c>
       <c r="E22" t="s">
-        <v>242</v>
+        <v>222</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>320</v>
+        <v>303</v>
       </c>
       <c r="G22" t="s">
-        <v>243</v>
+        <v>223</v>
       </c>
       <c r="H22" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.2">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="23" spans="2:8" ht="17" x14ac:dyDescent="0.2">
       <c r="B23" t="s">
         <v>29</v>
       </c>
       <c r="C23" t="s">
-        <v>46</v>
+        <v>225</v>
       </c>
       <c r="D23" t="s">
-        <v>47</v>
+        <v>226</v>
       </c>
       <c r="E23" t="s">
-        <v>48</v>
+        <v>222</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>321</v>
-      </c>
-      <c r="G23" t="s">
-        <v>54</v>
+        <v>303</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>282</v>
       </c>
       <c r="H23" t="s">
-        <v>55</v>
+        <v>227</v>
       </c>
     </row>
     <row r="24" spans="2:8" x14ac:dyDescent="0.2">
@@ -2018,68 +2048,68 @@
         <v>29</v>
       </c>
       <c r="C24" t="s">
-        <v>49</v>
+        <v>200</v>
       </c>
       <c r="D24" t="s">
-        <v>50</v>
+        <v>228</v>
       </c>
       <c r="E24" t="s">
-        <v>48</v>
+        <v>229</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>321</v>
+        <v>304</v>
       </c>
       <c r="G24" t="s">
-        <v>56</v>
+        <v>230</v>
       </c>
       <c r="H24" t="s">
-        <v>57</v>
+        <v>231</v>
       </c>
     </row>
     <row r="25" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B25" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C25" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="D25" t="s">
+        <v>45</v>
+      </c>
+      <c r="E25" t="s">
+        <v>46</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="G25" t="s">
         <v>52</v>
       </c>
-      <c r="E25" t="s">
+      <c r="H25" t="s">
         <v>53</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>322</v>
-      </c>
-      <c r="G25" t="s">
-        <v>58</v>
-      </c>
-      <c r="H25" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="26" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B26" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C26" t="s">
-        <v>146</v>
+        <v>47</v>
       </c>
       <c r="D26" t="s">
-        <v>168</v>
+        <v>48</v>
       </c>
       <c r="E26" t="s">
-        <v>169</v>
+        <v>46</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>323</v>
+        <v>305</v>
       </c>
       <c r="G26" t="s">
-        <v>170</v>
+        <v>54</v>
       </c>
       <c r="H26" t="s">
-        <v>171</v>
+        <v>55</v>
       </c>
     </row>
     <row r="27" spans="2:8" x14ac:dyDescent="0.2">
@@ -2087,22 +2117,22 @@
         <v>28</v>
       </c>
       <c r="C27" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="D27" t="s">
-        <v>6</v>
+        <v>50</v>
       </c>
       <c r="E27" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>324</v>
+        <v>306</v>
       </c>
       <c r="G27" t="s">
-        <v>7</v>
+        <v>56</v>
       </c>
       <c r="H27" t="s">
-        <v>204</v>
+        <v>57</v>
       </c>
     </row>
     <row r="28" spans="2:8" x14ac:dyDescent="0.2">
@@ -2110,22 +2140,22 @@
         <v>28</v>
       </c>
       <c r="C28" t="s">
-        <v>245</v>
+        <v>140</v>
       </c>
       <c r="D28" t="s">
-        <v>246</v>
+        <v>160</v>
       </c>
       <c r="E28" t="s">
-        <v>247</v>
+        <v>161</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>325</v>
+        <v>307</v>
       </c>
       <c r="G28" t="s">
-        <v>248</v>
+        <v>162</v>
       </c>
       <c r="H28" t="s">
-        <v>249</v>
+        <v>163</v>
       </c>
     </row>
     <row r="29" spans="2:8" x14ac:dyDescent="0.2">
@@ -2133,22 +2163,22 @@
         <v>28</v>
       </c>
       <c r="C29" t="s">
-        <v>207</v>
+        <v>58</v>
       </c>
       <c r="D29" t="s">
-        <v>250</v>
+        <v>6</v>
       </c>
       <c r="E29" t="s">
-        <v>247</v>
+        <v>59</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>325</v>
+        <v>308</v>
       </c>
       <c r="G29" t="s">
-        <v>251</v>
+        <v>7</v>
       </c>
       <c r="H29" t="s">
-        <v>252</v>
+        <v>196</v>
       </c>
     </row>
     <row r="30" spans="2:8" x14ac:dyDescent="0.2">
@@ -2156,22 +2186,22 @@
         <v>28</v>
       </c>
       <c r="C30" t="s">
-        <v>253</v>
+        <v>232</v>
       </c>
       <c r="D30" t="s">
-        <v>254</v>
+        <v>233</v>
       </c>
       <c r="E30" t="s">
-        <v>255</v>
+        <v>234</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>325</v>
+        <v>309</v>
       </c>
       <c r="G30" t="s">
-        <v>256</v>
+        <v>235</v>
       </c>
       <c r="H30" t="s">
-        <v>257</v>
+        <v>236</v>
       </c>
     </row>
     <row r="31" spans="2:8" x14ac:dyDescent="0.2">
@@ -2179,22 +2209,22 @@
         <v>28</v>
       </c>
       <c r="C31" t="s">
-        <v>258</v>
+        <v>199</v>
       </c>
       <c r="D31" t="s">
-        <v>259</v>
+        <v>237</v>
       </c>
       <c r="E31" t="s">
-        <v>247</v>
+        <v>234</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>325</v>
+        <v>309</v>
       </c>
       <c r="G31" t="s">
-        <v>260</v>
+        <v>238</v>
       </c>
       <c r="H31" t="s">
-        <v>261</v>
+        <v>239</v>
       </c>
     </row>
     <row r="32" spans="2:8" x14ac:dyDescent="0.2">
@@ -2202,22 +2232,22 @@
         <v>28</v>
       </c>
       <c r="C32" t="s">
-        <v>262</v>
+        <v>240</v>
       </c>
       <c r="D32" t="s">
-        <v>263</v>
+        <v>241</v>
       </c>
       <c r="E32" t="s">
-        <v>255</v>
+        <v>242</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>325</v>
+        <v>309</v>
       </c>
       <c r="G32" t="s">
-        <v>264</v>
+        <v>243</v>
       </c>
       <c r="H32" t="s">
-        <v>265</v>
+        <v>244</v>
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.2">
@@ -2225,22 +2255,22 @@
         <v>28</v>
       </c>
       <c r="C33" t="s">
-        <v>266</v>
+        <v>245</v>
       </c>
       <c r="D33" t="s">
-        <v>267</v>
+        <v>246</v>
       </c>
       <c r="E33" t="s">
-        <v>268</v>
+        <v>234</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>326</v>
+        <v>309</v>
       </c>
       <c r="G33" t="s">
-        <v>269</v>
+        <v>247</v>
       </c>
       <c r="H33" t="s">
-        <v>270</v>
+        <v>248</v>
       </c>
     </row>
     <row r="34" spans="2:8" x14ac:dyDescent="0.2">
@@ -2248,22 +2278,22 @@
         <v>28</v>
       </c>
       <c r="C34" t="s">
-        <v>271</v>
+        <v>249</v>
       </c>
       <c r="D34" t="s">
-        <v>272</v>
+        <v>250</v>
       </c>
       <c r="E34" t="s">
-        <v>273</v>
+        <v>242</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>327</v>
+        <v>309</v>
       </c>
       <c r="G34" t="s">
-        <v>274</v>
+        <v>251</v>
       </c>
       <c r="H34" t="s">
-        <v>275</v>
+        <v>252</v>
       </c>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.2">
@@ -2271,114 +2301,114 @@
         <v>28</v>
       </c>
       <c r="C35" t="s">
-        <v>62</v>
+        <v>253</v>
       </c>
       <c r="D35" t="s">
-        <v>63</v>
+        <v>254</v>
       </c>
       <c r="E35" t="s">
-        <v>64</v>
+        <v>255</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>328</v>
+        <v>310</v>
       </c>
       <c r="G35" t="s">
-        <v>65</v>
+        <v>256</v>
       </c>
       <c r="H35" t="s">
-        <v>66</v>
+        <v>257</v>
       </c>
     </row>
     <row r="36" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B36" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C36" t="s">
-        <v>67</v>
+        <v>258</v>
       </c>
       <c r="D36" t="s">
-        <v>68</v>
+        <v>259</v>
       </c>
       <c r="E36" t="s">
-        <v>179</v>
+        <v>260</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>329</v>
+        <v>311</v>
       </c>
       <c r="G36" t="s">
-        <v>77</v>
+        <v>261</v>
       </c>
       <c r="H36" t="s">
-        <v>78</v>
+        <v>262</v>
       </c>
     </row>
     <row r="37" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B37" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C37" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="D37" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="E37" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>330</v>
+        <v>312</v>
       </c>
       <c r="G37" t="s">
-        <v>79</v>
+        <v>63</v>
       </c>
       <c r="H37" t="s">
-        <v>80</v>
+        <v>64</v>
       </c>
     </row>
     <row r="38" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B38" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C38" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="D38" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="E38" t="s">
-        <v>73</v>
+        <v>171</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>331</v>
+        <v>313</v>
       </c>
       <c r="G38" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H38" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
     </row>
     <row r="39" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B39" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C39" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="D39" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="E39" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>332</v>
+        <v>314</v>
       </c>
       <c r="G39" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="H39" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
     </row>
     <row r="40" spans="2:8" x14ac:dyDescent="0.2">
@@ -2386,22 +2416,22 @@
         <v>28</v>
       </c>
       <c r="C40" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="D40" t="s">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="E40" t="s">
-        <v>300</v>
+        <v>71</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>333</v>
+        <v>315</v>
       </c>
       <c r="G40" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H40" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
     </row>
     <row r="41" spans="2:8" x14ac:dyDescent="0.2">
@@ -2409,252 +2439,252 @@
         <v>28</v>
       </c>
       <c r="C41" t="s">
-        <v>276</v>
+        <v>72</v>
       </c>
       <c r="D41" t="s">
-        <v>277</v>
+        <v>73</v>
       </c>
       <c r="E41" t="s">
-        <v>300</v>
+        <v>74</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>333</v>
+        <v>316</v>
       </c>
       <c r="G41" t="s">
-        <v>301</v>
+        <v>81</v>
       </c>
       <c r="H41" t="s">
-        <v>278</v>
+        <v>82</v>
       </c>
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B42" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C42" t="s">
-        <v>279</v>
+        <v>83</v>
       </c>
       <c r="D42" t="s">
-        <v>280</v>
+        <v>84</v>
       </c>
       <c r="E42" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>334</v>
+        <v>317</v>
       </c>
       <c r="G42" t="s">
-        <v>282</v>
+        <v>85</v>
       </c>
       <c r="H42" t="s">
-        <v>283</v>
+        <v>86</v>
       </c>
     </row>
     <row r="43" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B43" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C43" t="s">
+        <v>263</v>
+      </c>
+      <c r="D43" t="s">
+        <v>264</v>
+      </c>
+      <c r="E43" t="s">
         <v>284</v>
       </c>
-      <c r="D43" t="s">
+      <c r="F43" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="G43" t="s">
         <v>285</v>
       </c>
-      <c r="E43" t="s">
-        <v>286</v>
-      </c>
-      <c r="F43" s="3" t="s">
-        <v>335</v>
-      </c>
-      <c r="G43" t="s">
-        <v>287</v>
-      </c>
       <c r="H43" t="s">
-        <v>288</v>
+        <v>265</v>
       </c>
     </row>
     <row r="44" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B44" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C44" t="s">
-        <v>172</v>
+        <v>266</v>
       </c>
       <c r="D44" t="s">
-        <v>173</v>
+        <v>267</v>
       </c>
       <c r="E44" t="s">
-        <v>174</v>
+        <v>268</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>336</v>
+        <v>318</v>
       </c>
       <c r="G44" t="s">
-        <v>175</v>
+        <v>269</v>
       </c>
       <c r="H44" t="s">
-        <v>176</v>
+        <v>270</v>
       </c>
     </row>
     <row r="45" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B45" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C45" t="s">
-        <v>100</v>
+        <v>271</v>
       </c>
       <c r="D45" t="s">
-        <v>289</v>
+        <v>272</v>
       </c>
       <c r="E45" t="s">
-        <v>290</v>
+        <v>273</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>337</v>
+        <v>319</v>
       </c>
       <c r="G45" t="s">
-        <v>302</v>
+        <v>274</v>
       </c>
       <c r="H45" t="s">
-        <v>291</v>
+        <v>275</v>
       </c>
     </row>
     <row r="46" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B46" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C46" t="s">
-        <v>89</v>
+        <v>359</v>
       </c>
       <c r="D46" t="s">
-        <v>90</v>
+        <v>360</v>
       </c>
       <c r="E46" t="s">
-        <v>91</v>
+        <v>361</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>338</v>
+        <v>362</v>
       </c>
       <c r="G46" t="s">
-        <v>92</v>
+        <v>363</v>
       </c>
       <c r="H46" t="s">
-        <v>93</v>
+        <v>196</v>
       </c>
     </row>
     <row r="47" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B47" t="s">
-        <v>145</v>
+        <v>28</v>
       </c>
       <c r="C47" t="s">
-        <v>146</v>
+        <v>164</v>
       </c>
       <c r="D47" t="s">
-        <v>181</v>
+        <v>165</v>
       </c>
       <c r="E47" t="s">
-        <v>147</v>
+        <v>166</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>339</v>
+        <v>320</v>
       </c>
       <c r="G47" t="s">
-        <v>182</v>
+        <v>167</v>
       </c>
       <c r="H47" t="s">
-        <v>183</v>
+        <v>168</v>
       </c>
     </row>
     <row r="48" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B48" t="s">
-        <v>145</v>
+        <v>28</v>
       </c>
       <c r="C48" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="D48" t="s">
-        <v>63</v>
+        <v>276</v>
       </c>
       <c r="E48" t="s">
-        <v>147</v>
+        <v>277</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>339</v>
+        <v>321</v>
       </c>
       <c r="G48" t="s">
-        <v>65</v>
+        <v>286</v>
       </c>
       <c r="H48" t="s">
-        <v>66</v>
+        <v>278</v>
       </c>
     </row>
     <row r="49" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B49" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C49" t="s">
-        <v>109</v>
+        <v>346</v>
       </c>
       <c r="D49" t="s">
-        <v>4</v>
+        <v>347</v>
       </c>
       <c r="E49" t="s">
-        <v>110</v>
+        <v>87</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>340</v>
+        <v>354</v>
       </c>
       <c r="G49" t="s">
-        <v>133</v>
+        <v>280</v>
       </c>
       <c r="H49" t="s">
-        <v>134</v>
+        <v>348</v>
       </c>
     </row>
     <row r="50" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B50" t="s">
-        <v>30</v>
+        <v>139</v>
       </c>
       <c r="C50" t="s">
-        <v>97</v>
+        <v>140</v>
       </c>
       <c r="D50" t="s">
-        <v>98</v>
+        <v>173</v>
       </c>
       <c r="E50" t="s">
-        <v>99</v>
+        <v>141</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>341</v>
+        <v>322</v>
       </c>
       <c r="G50" t="s">
-        <v>125</v>
+        <v>174</v>
       </c>
       <c r="H50" t="s">
-        <v>126</v>
+        <v>175</v>
       </c>
     </row>
     <row r="51" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B51" t="s">
-        <v>30</v>
+        <v>139</v>
       </c>
       <c r="C51" t="s">
-        <v>94</v>
+        <v>60</v>
       </c>
       <c r="D51" t="s">
-        <v>95</v>
+        <v>61</v>
       </c>
       <c r="E51" t="s">
-        <v>205</v>
+        <v>141</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>342</v>
+        <v>322</v>
       </c>
       <c r="G51" t="s">
-        <v>5</v>
+        <v>63</v>
       </c>
       <c r="H51" t="s">
-        <v>96</v>
+        <v>64</v>
       </c>
     </row>
     <row r="52" spans="2:8" x14ac:dyDescent="0.2">
@@ -2662,16 +2692,16 @@
         <v>30</v>
       </c>
       <c r="C52" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="D52" t="s">
-        <v>101</v>
+        <v>4</v>
       </c>
       <c r="E52" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>343</v>
+        <v>323</v>
       </c>
       <c r="G52" t="s">
         <v>127</v>
@@ -2685,22 +2715,22 @@
         <v>30</v>
       </c>
       <c r="C53" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="D53" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="E53" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>344</v>
+        <v>324</v>
       </c>
       <c r="G53" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="H53" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
     </row>
     <row r="54" spans="2:8" x14ac:dyDescent="0.2">
@@ -2708,22 +2738,22 @@
         <v>30</v>
       </c>
       <c r="C54" t="s">
-        <v>106</v>
+        <v>88</v>
       </c>
       <c r="D54" t="s">
-        <v>107</v>
+        <v>89</v>
       </c>
       <c r="E54" t="s">
-        <v>108</v>
+        <v>197</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>345</v>
+        <v>325</v>
       </c>
       <c r="G54" t="s">
-        <v>131</v>
+        <v>5</v>
       </c>
       <c r="H54" t="s">
-        <v>132</v>
+        <v>90</v>
       </c>
     </row>
     <row r="55" spans="2:8" x14ac:dyDescent="0.2">
@@ -2731,22 +2761,22 @@
         <v>30</v>
       </c>
       <c r="C55" t="s">
-        <v>111</v>
+        <v>94</v>
       </c>
       <c r="D55" t="s">
-        <v>112</v>
+        <v>95</v>
       </c>
       <c r="E55" t="s">
-        <v>113</v>
+        <v>96</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>346</v>
+        <v>326</v>
       </c>
       <c r="G55" t="s">
-        <v>135</v>
+        <v>121</v>
       </c>
       <c r="H55" t="s">
-        <v>136</v>
+        <v>122</v>
       </c>
     </row>
     <row r="56" spans="2:8" x14ac:dyDescent="0.2">
@@ -2754,22 +2784,22 @@
         <v>30</v>
       </c>
       <c r="C56" t="s">
-        <v>114</v>
+        <v>97</v>
       </c>
       <c r="D56" t="s">
-        <v>115</v>
+        <v>98</v>
       </c>
       <c r="E56" t="s">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>347</v>
+        <v>327</v>
       </c>
       <c r="G56" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
       <c r="H56" t="s">
-        <v>138</v>
+        <v>124</v>
       </c>
     </row>
     <row r="57" spans="2:8" x14ac:dyDescent="0.2">
@@ -2777,22 +2807,22 @@
         <v>30</v>
       </c>
       <c r="C57" t="s">
-        <v>117</v>
+        <v>100</v>
       </c>
       <c r="D57" t="s">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="E57" t="s">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>119</v>
+        <v>328</v>
       </c>
       <c r="G57" t="s">
-        <v>139</v>
+        <v>125</v>
       </c>
       <c r="H57" t="s">
-        <v>140</v>
+        <v>126</v>
       </c>
     </row>
     <row r="58" spans="2:8" x14ac:dyDescent="0.2">
@@ -2800,22 +2830,22 @@
         <v>30</v>
       </c>
       <c r="C58" t="s">
-        <v>120</v>
+        <v>105</v>
       </c>
       <c r="D58" t="s">
-        <v>121</v>
+        <v>106</v>
       </c>
       <c r="E58" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>119</v>
+        <v>329</v>
       </c>
       <c r="G58" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
       <c r="H58" t="s">
-        <v>142</v>
+        <v>130</v>
       </c>
     </row>
     <row r="59" spans="2:8" x14ac:dyDescent="0.2">
@@ -2823,22 +2853,22 @@
         <v>30</v>
       </c>
       <c r="C59" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="D59" t="s">
-        <v>123</v>
+        <v>109</v>
       </c>
       <c r="E59" t="s">
-        <v>124</v>
+        <v>110</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>348</v>
+        <v>330</v>
       </c>
       <c r="G59" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
       <c r="H59" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
     </row>
     <row r="60" spans="2:8" x14ac:dyDescent="0.2">
@@ -2846,160 +2876,298 @@
         <v>30</v>
       </c>
       <c r="C60" t="s">
-        <v>148</v>
+        <v>111</v>
       </c>
       <c r="D60" t="s">
-        <v>149</v>
+        <v>112</v>
       </c>
       <c r="E60" t="s">
-        <v>150</v>
+        <v>113</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>349</v>
+        <v>113</v>
       </c>
       <c r="G60" t="s">
-        <v>151</v>
+        <v>133</v>
       </c>
       <c r="H60" t="s">
-        <v>152</v>
+        <v>134</v>
       </c>
     </row>
     <row r="61" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B61" t="s">
-        <v>177</v>
+        <v>30</v>
       </c>
       <c r="C61" t="s">
-        <v>67</v>
+        <v>114</v>
       </c>
       <c r="D61" t="s">
-        <v>68</v>
+        <v>115</v>
       </c>
       <c r="E61" t="s">
-        <v>178</v>
+        <v>113</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>350</v>
+        <v>113</v>
       </c>
       <c r="G61" t="s">
-        <v>77</v>
+        <v>135</v>
       </c>
       <c r="H61" t="s">
-        <v>78</v>
+        <v>136</v>
       </c>
     </row>
     <row r="62" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B62" t="s">
-        <v>177</v>
+        <v>30</v>
       </c>
       <c r="C62" t="s">
-        <v>292</v>
+        <v>116</v>
       </c>
       <c r="D62" t="s">
-        <v>293</v>
+        <v>117</v>
       </c>
       <c r="E62" t="s">
-        <v>294</v>
+        <v>118</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>351</v>
+        <v>331</v>
       </c>
       <c r="G62" t="s">
-        <v>296</v>
+        <v>137</v>
       </c>
       <c r="H62" t="s">
-        <v>295</v>
+        <v>138</v>
       </c>
     </row>
     <row r="63" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B63" t="s">
-        <v>185</v>
+        <v>30</v>
       </c>
       <c r="C63" t="s">
-        <v>186</v>
+        <v>142</v>
       </c>
       <c r="D63" t="s">
-        <v>187</v>
+        <v>143</v>
       </c>
       <c r="E63" t="s">
-        <v>188</v>
+        <v>144</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>352</v>
+        <v>332</v>
       </c>
       <c r="G63" t="s">
-        <v>194</v>
+        <v>145</v>
       </c>
       <c r="H63" t="s">
-        <v>204</v>
+        <v>146</v>
       </c>
     </row>
     <row r="64" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B64" t="s">
-        <v>185</v>
+        <v>30</v>
       </c>
       <c r="C64" t="s">
-        <v>189</v>
+        <v>349</v>
       </c>
       <c r="D64" t="s">
-        <v>190</v>
+        <v>89</v>
       </c>
       <c r="E64" t="s">
-        <v>191</v>
+        <v>350</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="G64" t="s">
-        <v>195</v>
+        <v>351</v>
       </c>
       <c r="H64" t="s">
-        <v>204</v>
+        <v>356</v>
       </c>
     </row>
     <row r="65" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B65" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="C65" t="s">
-        <v>197</v>
+        <v>164</v>
       </c>
       <c r="D65" t="s">
-        <v>198</v>
+        <v>165</v>
       </c>
       <c r="E65" t="s">
-        <v>199</v>
+        <v>353</v>
       </c>
       <c r="F65" s="3" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="G65" t="s">
-        <v>202</v>
+        <v>167</v>
       </c>
       <c r="H65" t="s">
-        <v>204</v>
+        <v>168</v>
       </c>
     </row>
     <row r="66" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B66" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="C66" t="s">
-        <v>163</v>
+        <v>338</v>
       </c>
       <c r="D66" t="s">
-        <v>200</v>
+        <v>339</v>
       </c>
       <c r="E66" t="s">
-        <v>201</v>
+        <v>279</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>314</v>
+        <v>334</v>
       </c>
       <c r="G66" t="s">
-        <v>203</v>
+        <v>364</v>
       </c>
       <c r="H66" t="s">
-        <v>204</v>
+        <v>340</v>
+      </c>
+    </row>
+    <row r="67" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B67" t="s">
+        <v>169</v>
+      </c>
+      <c r="C67" t="s">
+        <v>65</v>
+      </c>
+      <c r="D67" t="s">
+        <v>66</v>
+      </c>
+      <c r="E67" t="s">
+        <v>170</v>
+      </c>
+      <c r="F67" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="G67" t="s">
+        <v>75</v>
+      </c>
+      <c r="H67" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="68" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B68" t="s">
+        <v>169</v>
+      </c>
+      <c r="C68" t="s">
+        <v>39</v>
+      </c>
+      <c r="D68" t="s">
+        <v>40</v>
+      </c>
+      <c r="E68" t="s">
+        <v>358</v>
+      </c>
+      <c r="F68" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="G68" t="s">
+        <v>42</v>
+      </c>
+      <c r="H68" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="69" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B69" t="s">
+        <v>177</v>
+      </c>
+      <c r="C69" t="s">
+        <v>178</v>
+      </c>
+      <c r="D69" t="s">
+        <v>179</v>
+      </c>
+      <c r="E69" t="s">
+        <v>180</v>
+      </c>
+      <c r="F69" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="G69" t="s">
+        <v>186</v>
+      </c>
+      <c r="H69" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="70" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B70" t="s">
+        <v>177</v>
+      </c>
+      <c r="C70" t="s">
+        <v>181</v>
+      </c>
+      <c r="D70" t="s">
+        <v>182</v>
+      </c>
+      <c r="E70" t="s">
+        <v>183</v>
+      </c>
+      <c r="F70" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="G70" t="s">
+        <v>187</v>
+      </c>
+      <c r="H70" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="71" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B71" t="s">
+        <v>177</v>
+      </c>
+      <c r="C71" t="s">
+        <v>189</v>
+      </c>
+      <c r="D71" t="s">
+        <v>190</v>
+      </c>
+      <c r="E71" t="s">
+        <v>191</v>
+      </c>
+      <c r="F71" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="G71" t="s">
+        <v>194</v>
+      </c>
+      <c r="H71" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="72" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B72" t="s">
+        <v>177</v>
+      </c>
+      <c r="C72" t="s">
+        <v>155</v>
+      </c>
+      <c r="D72" t="s">
+        <v>192</v>
+      </c>
+      <c r="E72" t="s">
+        <v>193</v>
+      </c>
+      <c r="F72" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="G72" t="s">
+        <v>195</v>
+      </c>
+      <c r="H72" t="s">
+        <v>196</v>
       </c>
     </row>
   </sheetData>

--- a/data/liste-equipe.xlsx
+++ b/data/liste-equipe.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10119"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10209"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jeremylavalade/Library/CloudStorage/GoogleDrive-b00730264@essec.edu/Drive partagés/L'Harmonie du Doute/3. Services Supports/3. Com' Externe (hors financement)/2. Site Web/2. Site Web/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED4395DB-91DE-424B-8B07-CC792D6B448A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92D1F7A4-9A68-8545-8198-7A8653D944E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17740" xr2:uid="{786A410D-58C9-CF4E-A296-84671034DD88}"/>
   </bookViews>
@@ -629,9 +629,6 @@
     <t>contact@harmoniedudoutefilm.fr</t>
   </si>
   <si>
-    <t>Directrice de Relation Publique</t>
-  </si>
-  <si>
     <t>1er Assistant Mise-en-scène</t>
   </si>
   <si>
@@ -1131,6 +1128,9 @@
   </si>
   <si>
     <t>umbrella_visual</t>
+  </si>
+  <si>
+    <t>Directrice des Relations Publiques</t>
   </si>
 </sst>
 </file>
@@ -1548,7 +1548,7 @@
         <v>13</v>
       </c>
       <c r="F2" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="G2" t="s">
         <v>2</v>
@@ -1574,7 +1574,7 @@
         <v>11</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="G3" t="s">
         <v>19</v>
@@ -1597,7 +1597,7 @@
         <v>16</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="G4" t="s">
         <v>17</v>
@@ -1620,7 +1620,7 @@
         <v>23</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>25</v>
@@ -1643,7 +1643,7 @@
         <v>24</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="G6" t="s">
         <v>188</v>
@@ -1666,7 +1666,7 @@
         <v>24</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="G7" t="s">
         <v>149</v>
@@ -1686,13 +1686,13 @@
         <v>151</v>
       </c>
       <c r="E8" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="G8" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H8" t="s">
         <v>196</v>
@@ -1703,22 +1703,22 @@
         <v>28</v>
       </c>
       <c r="C9" t="s">
+        <v>198</v>
+      </c>
+      <c r="D9" t="s">
         <v>199</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>200</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="G9" t="s">
         <v>201</v>
       </c>
-      <c r="F9" s="3" t="s">
-        <v>293</v>
-      </c>
-      <c r="G9" t="s">
+      <c r="H9" t="s">
         <v>202</v>
-      </c>
-      <c r="H9" t="s">
-        <v>203</v>
       </c>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.2">
@@ -1726,22 +1726,22 @@
         <v>28</v>
       </c>
       <c r="C10" t="s">
+        <v>203</v>
+      </c>
+      <c r="D10" t="s">
         <v>204</v>
       </c>
-      <c r="D10" t="s">
+      <c r="E10" t="s">
         <v>205</v>
       </c>
-      <c r="E10" t="s">
+      <c r="F10" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="G10" t="s">
         <v>206</v>
       </c>
-      <c r="F10" s="3" t="s">
-        <v>294</v>
-      </c>
-      <c r="G10" t="s">
+      <c r="H10" t="s">
         <v>207</v>
-      </c>
-      <c r="H10" t="s">
-        <v>208</v>
       </c>
     </row>
     <row r="11" spans="2:10" x14ac:dyDescent="0.2">
@@ -1758,7 +1758,7 @@
         <v>33</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="G11" t="s">
         <v>37</v>
@@ -1781,10 +1781,10 @@
         <v>36</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="G12" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H12" t="s">
         <v>196</v>
@@ -1804,10 +1804,10 @@
         <v>172</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="G13" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H13" t="s">
         <v>196</v>
@@ -1818,19 +1818,19 @@
         <v>27</v>
       </c>
       <c r="C14" t="s">
+        <v>340</v>
+      </c>
+      <c r="D14" t="s">
         <v>341</v>
-      </c>
-      <c r="D14" t="s">
-        <v>342</v>
       </c>
       <c r="E14" t="s">
         <v>152</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="G14" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H14" t="s">
         <v>196</v>
@@ -1841,19 +1841,19 @@
         <v>27</v>
       </c>
       <c r="C15" t="s">
+        <v>342</v>
+      </c>
+      <c r="D15" t="s">
         <v>343</v>
-      </c>
-      <c r="D15" t="s">
-        <v>344</v>
       </c>
       <c r="E15" t="s">
         <v>152</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="G15" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H15" t="s">
         <v>196</v>
@@ -1864,19 +1864,19 @@
         <v>27</v>
       </c>
       <c r="C16" t="s">
+        <v>208</v>
+      </c>
+      <c r="D16" t="s">
         <v>209</v>
-      </c>
-      <c r="D16" t="s">
-        <v>210</v>
       </c>
       <c r="E16" t="s">
         <v>152</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="G16" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H16" t="s">
         <v>196</v>
@@ -1887,19 +1887,19 @@
         <v>27</v>
       </c>
       <c r="C17" t="s">
+        <v>210</v>
+      </c>
+      <c r="D17" t="s">
         <v>211</v>
-      </c>
-      <c r="D17" t="s">
-        <v>212</v>
       </c>
       <c r="E17" t="s">
         <v>152</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="G17" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H17" t="s">
         <v>196</v>
@@ -1919,7 +1919,7 @@
         <v>41</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="G18" t="s">
         <v>42</v>
@@ -1942,7 +1942,7 @@
         <v>157</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="G19" t="s">
         <v>158</v>
@@ -1956,22 +1956,22 @@
         <v>29</v>
       </c>
       <c r="C20" t="s">
+        <v>212</v>
+      </c>
+      <c r="D20" t="s">
         <v>213</v>
       </c>
-      <c r="D20" t="s">
+      <c r="E20" t="s">
+        <v>280</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="G20" t="s">
         <v>214</v>
       </c>
-      <c r="E20" t="s">
-        <v>281</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>301</v>
-      </c>
-      <c r="G20" t="s">
+      <c r="H20" t="s">
         <v>215</v>
-      </c>
-      <c r="H20" t="s">
-        <v>216</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.2">
@@ -1979,22 +1979,22 @@
         <v>29</v>
       </c>
       <c r="C21" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D21" t="s">
+        <v>216</v>
+      </c>
+      <c r="E21" t="s">
         <v>217</v>
       </c>
-      <c r="E21" t="s">
+      <c r="F21" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="G21" t="s">
         <v>218</v>
       </c>
-      <c r="F21" s="3" t="s">
-        <v>302</v>
-      </c>
-      <c r="G21" t="s">
-        <v>219</v>
-      </c>
       <c r="H21" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.2">
@@ -2002,22 +2002,22 @@
         <v>29</v>
       </c>
       <c r="C22" t="s">
+        <v>219</v>
+      </c>
+      <c r="D22" t="s">
         <v>220</v>
       </c>
-      <c r="D22" t="s">
+      <c r="E22" t="s">
         <v>221</v>
       </c>
-      <c r="E22" t="s">
+      <c r="F22" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="G22" t="s">
         <v>222</v>
       </c>
-      <c r="F22" s="3" t="s">
-        <v>303</v>
-      </c>
-      <c r="G22" t="s">
+      <c r="H22" t="s">
         <v>223</v>
-      </c>
-      <c r="H22" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="23" spans="2:8" ht="17" x14ac:dyDescent="0.2">
@@ -2025,22 +2025,22 @@
         <v>29</v>
       </c>
       <c r="C23" t="s">
+        <v>224</v>
+      </c>
+      <c r="D23" t="s">
         <v>225</v>
       </c>
-      <c r="D23" t="s">
+      <c r="E23" t="s">
+        <v>221</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="H23" t="s">
         <v>226</v>
-      </c>
-      <c r="E23" t="s">
-        <v>222</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>303</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="H23" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="24" spans="2:8" x14ac:dyDescent="0.2">
@@ -2048,22 +2048,22 @@
         <v>29</v>
       </c>
       <c r="C24" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D24" t="s">
+        <v>227</v>
+      </c>
+      <c r="E24" t="s">
         <v>228</v>
       </c>
-      <c r="E24" t="s">
+      <c r="F24" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="G24" t="s">
         <v>229</v>
       </c>
-      <c r="F24" s="3" t="s">
-        <v>304</v>
-      </c>
-      <c r="G24" t="s">
+      <c r="H24" t="s">
         <v>230</v>
-      </c>
-      <c r="H24" t="s">
-        <v>231</v>
       </c>
     </row>
     <row r="25" spans="2:8" x14ac:dyDescent="0.2">
@@ -2080,7 +2080,7 @@
         <v>46</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="G25" t="s">
         <v>52</v>
@@ -2103,7 +2103,7 @@
         <v>46</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="G26" t="s">
         <v>54</v>
@@ -2126,7 +2126,7 @@
         <v>51</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="G27" t="s">
         <v>56</v>
@@ -2149,7 +2149,7 @@
         <v>161</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="G28" t="s">
         <v>162</v>
@@ -2172,7 +2172,7 @@
         <v>59</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="G29" t="s">
         <v>7</v>
@@ -2186,22 +2186,22 @@
         <v>28</v>
       </c>
       <c r="C30" t="s">
+        <v>231</v>
+      </c>
+      <c r="D30" t="s">
         <v>232</v>
       </c>
-      <c r="D30" t="s">
+      <c r="E30" t="s">
         <v>233</v>
       </c>
-      <c r="E30" t="s">
+      <c r="F30" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="G30" t="s">
         <v>234</v>
       </c>
-      <c r="F30" s="3" t="s">
-        <v>309</v>
-      </c>
-      <c r="G30" t="s">
+      <c r="H30" t="s">
         <v>235</v>
-      </c>
-      <c r="H30" t="s">
-        <v>236</v>
       </c>
     </row>
     <row r="31" spans="2:8" x14ac:dyDescent="0.2">
@@ -2209,22 +2209,22 @@
         <v>28</v>
       </c>
       <c r="C31" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D31" t="s">
+        <v>236</v>
+      </c>
+      <c r="E31" t="s">
+        <v>233</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="G31" t="s">
         <v>237</v>
       </c>
-      <c r="E31" t="s">
-        <v>234</v>
-      </c>
-      <c r="F31" s="3" t="s">
-        <v>309</v>
-      </c>
-      <c r="G31" t="s">
+      <c r="H31" t="s">
         <v>238</v>
-      </c>
-      <c r="H31" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="32" spans="2:8" x14ac:dyDescent="0.2">
@@ -2232,22 +2232,22 @@
         <v>28</v>
       </c>
       <c r="C32" t="s">
+        <v>239</v>
+      </c>
+      <c r="D32" t="s">
         <v>240</v>
       </c>
-      <c r="D32" t="s">
+      <c r="E32" t="s">
         <v>241</v>
       </c>
-      <c r="E32" t="s">
+      <c r="F32" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="G32" t="s">
         <v>242</v>
       </c>
-      <c r="F32" s="3" t="s">
-        <v>309</v>
-      </c>
-      <c r="G32" t="s">
+      <c r="H32" t="s">
         <v>243</v>
-      </c>
-      <c r="H32" t="s">
-        <v>244</v>
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.2">
@@ -2255,22 +2255,22 @@
         <v>28</v>
       </c>
       <c r="C33" t="s">
+        <v>244</v>
+      </c>
+      <c r="D33" t="s">
         <v>245</v>
       </c>
-      <c r="D33" t="s">
+      <c r="E33" t="s">
+        <v>233</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="G33" t="s">
         <v>246</v>
       </c>
-      <c r="E33" t="s">
-        <v>234</v>
-      </c>
-      <c r="F33" s="3" t="s">
-        <v>309</v>
-      </c>
-      <c r="G33" t="s">
+      <c r="H33" t="s">
         <v>247</v>
-      </c>
-      <c r="H33" t="s">
-        <v>248</v>
       </c>
     </row>
     <row r="34" spans="2:8" x14ac:dyDescent="0.2">
@@ -2278,22 +2278,22 @@
         <v>28</v>
       </c>
       <c r="C34" t="s">
+        <v>248</v>
+      </c>
+      <c r="D34" t="s">
         <v>249</v>
       </c>
-      <c r="D34" t="s">
+      <c r="E34" t="s">
+        <v>241</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="G34" t="s">
         <v>250</v>
       </c>
-      <c r="E34" t="s">
-        <v>242</v>
-      </c>
-      <c r="F34" s="3" t="s">
-        <v>309</v>
-      </c>
-      <c r="G34" t="s">
+      <c r="H34" t="s">
         <v>251</v>
-      </c>
-      <c r="H34" t="s">
-        <v>252</v>
       </c>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.2">
@@ -2301,22 +2301,22 @@
         <v>28</v>
       </c>
       <c r="C35" t="s">
+        <v>252</v>
+      </c>
+      <c r="D35" t="s">
         <v>253</v>
       </c>
-      <c r="D35" t="s">
+      <c r="E35" t="s">
         <v>254</v>
       </c>
-      <c r="E35" t="s">
+      <c r="F35" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="G35" t="s">
         <v>255</v>
       </c>
-      <c r="F35" s="3" t="s">
-        <v>310</v>
-      </c>
-      <c r="G35" t="s">
+      <c r="H35" t="s">
         <v>256</v>
-      </c>
-      <c r="H35" t="s">
-        <v>257</v>
       </c>
     </row>
     <row r="36" spans="2:8" x14ac:dyDescent="0.2">
@@ -2324,22 +2324,22 @@
         <v>28</v>
       </c>
       <c r="C36" t="s">
+        <v>257</v>
+      </c>
+      <c r="D36" t="s">
         <v>258</v>
       </c>
-      <c r="D36" t="s">
+      <c r="E36" t="s">
         <v>259</v>
       </c>
-      <c r="E36" t="s">
+      <c r="F36" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="G36" t="s">
         <v>260</v>
       </c>
-      <c r="F36" s="3" t="s">
-        <v>311</v>
-      </c>
-      <c r="G36" t="s">
+      <c r="H36" t="s">
         <v>261</v>
-      </c>
-      <c r="H36" t="s">
-        <v>262</v>
       </c>
     </row>
     <row r="37" spans="2:8" x14ac:dyDescent="0.2">
@@ -2356,7 +2356,7 @@
         <v>62</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="G37" t="s">
         <v>63</v>
@@ -2379,7 +2379,7 @@
         <v>171</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="G38" t="s">
         <v>75</v>
@@ -2402,7 +2402,7 @@
         <v>68</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="G39" t="s">
         <v>77</v>
@@ -2425,7 +2425,7 @@
         <v>71</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="G40" t="s">
         <v>79</v>
@@ -2448,7 +2448,7 @@
         <v>74</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="G41" t="s">
         <v>81</v>
@@ -2468,10 +2468,10 @@
         <v>84</v>
       </c>
       <c r="E42" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="G42" t="s">
         <v>85</v>
@@ -2485,22 +2485,22 @@
         <v>28</v>
       </c>
       <c r="C43" t="s">
+        <v>262</v>
+      </c>
+      <c r="D43" t="s">
         <v>263</v>
       </c>
-      <c r="D43" t="s">
+      <c r="E43" t="s">
+        <v>283</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="G43" t="s">
+        <v>284</v>
+      </c>
+      <c r="H43" t="s">
         <v>264</v>
-      </c>
-      <c r="E43" t="s">
-        <v>284</v>
-      </c>
-      <c r="F43" s="3" t="s">
-        <v>317</v>
-      </c>
-      <c r="G43" t="s">
-        <v>285</v>
-      </c>
-      <c r="H43" t="s">
-        <v>265</v>
       </c>
     </row>
     <row r="44" spans="2:8" x14ac:dyDescent="0.2">
@@ -2508,22 +2508,22 @@
         <v>29</v>
       </c>
       <c r="C44" t="s">
+        <v>265</v>
+      </c>
+      <c r="D44" t="s">
         <v>266</v>
       </c>
-      <c r="D44" t="s">
+      <c r="E44" t="s">
         <v>267</v>
       </c>
-      <c r="E44" t="s">
+      <c r="F44" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="G44" t="s">
         <v>268</v>
       </c>
-      <c r="F44" s="3" t="s">
-        <v>318</v>
-      </c>
-      <c r="G44" t="s">
+      <c r="H44" t="s">
         <v>269</v>
-      </c>
-      <c r="H44" t="s">
-        <v>270</v>
       </c>
     </row>
     <row r="45" spans="2:8" x14ac:dyDescent="0.2">
@@ -2531,22 +2531,22 @@
         <v>29</v>
       </c>
       <c r="C45" t="s">
+        <v>270</v>
+      </c>
+      <c r="D45" t="s">
         <v>271</v>
       </c>
-      <c r="D45" t="s">
+      <c r="E45" t="s">
         <v>272</v>
       </c>
-      <c r="E45" t="s">
+      <c r="F45" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="G45" t="s">
         <v>273</v>
       </c>
-      <c r="F45" s="3" t="s">
-        <v>319</v>
-      </c>
-      <c r="G45" t="s">
+      <c r="H45" t="s">
         <v>274</v>
-      </c>
-      <c r="H45" t="s">
-        <v>275</v>
       </c>
     </row>
     <row r="46" spans="2:8" x14ac:dyDescent="0.2">
@@ -2554,19 +2554,19 @@
         <v>29</v>
       </c>
       <c r="C46" t="s">
+        <v>358</v>
+      </c>
+      <c r="D46" t="s">
         <v>359</v>
       </c>
-      <c r="D46" t="s">
+      <c r="E46" t="s">
         <v>360</v>
       </c>
-      <c r="E46" t="s">
+      <c r="F46" s="3" t="s">
         <v>361</v>
       </c>
-      <c r="F46" s="3" t="s">
+      <c r="G46" t="s">
         <v>362</v>
-      </c>
-      <c r="G46" t="s">
-        <v>363</v>
       </c>
       <c r="H46" t="s">
         <v>196</v>
@@ -2586,7 +2586,7 @@
         <v>166</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="G47" t="s">
         <v>167</v>
@@ -2603,19 +2603,19 @@
         <v>94</v>
       </c>
       <c r="D48" t="s">
+        <v>275</v>
+      </c>
+      <c r="E48" t="s">
         <v>276</v>
       </c>
-      <c r="E48" t="s">
+      <c r="F48" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="G48" t="s">
+        <v>285</v>
+      </c>
+      <c r="H48" t="s">
         <v>277</v>
-      </c>
-      <c r="F48" s="3" t="s">
-        <v>321</v>
-      </c>
-      <c r="G48" t="s">
-        <v>286</v>
-      </c>
-      <c r="H48" t="s">
-        <v>278</v>
       </c>
     </row>
     <row r="49" spans="2:8" x14ac:dyDescent="0.2">
@@ -2623,22 +2623,22 @@
         <v>28</v>
       </c>
       <c r="C49" t="s">
+        <v>345</v>
+      </c>
+      <c r="D49" t="s">
         <v>346</v>
-      </c>
-      <c r="D49" t="s">
-        <v>347</v>
       </c>
       <c r="E49" t="s">
         <v>87</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="G49" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H49" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="50" spans="2:8" x14ac:dyDescent="0.2">
@@ -2655,7 +2655,7 @@
         <v>141</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="G50" t="s">
         <v>174</v>
@@ -2678,7 +2678,7 @@
         <v>141</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="G51" t="s">
         <v>63</v>
@@ -2701,7 +2701,7 @@
         <v>104</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G52" t="s">
         <v>127</v>
@@ -2724,7 +2724,7 @@
         <v>93</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="G53" t="s">
         <v>119</v>
@@ -2744,10 +2744,10 @@
         <v>89</v>
       </c>
       <c r="E54" t="s">
-        <v>197</v>
+        <v>364</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="G54" t="s">
         <v>5</v>
@@ -2770,7 +2770,7 @@
         <v>96</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="G55" t="s">
         <v>121</v>
@@ -2793,7 +2793,7 @@
         <v>99</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="G56" t="s">
         <v>123</v>
@@ -2816,7 +2816,7 @@
         <v>102</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="G57" t="s">
         <v>125</v>
@@ -2839,7 +2839,7 @@
         <v>107</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="G58" t="s">
         <v>129</v>
@@ -2862,7 +2862,7 @@
         <v>110</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="G59" t="s">
         <v>131</v>
@@ -2931,7 +2931,7 @@
         <v>118</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="G62" t="s">
         <v>137</v>
@@ -2954,7 +2954,7 @@
         <v>144</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="G63" t="s">
         <v>145</v>
@@ -2968,22 +2968,22 @@
         <v>30</v>
       </c>
       <c r="C64" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="D64" t="s">
         <v>89</v>
       </c>
       <c r="E64" t="s">
+        <v>349</v>
+      </c>
+      <c r="F64" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="G64" t="s">
         <v>350</v>
       </c>
-      <c r="F64" s="3" t="s">
-        <v>352</v>
-      </c>
-      <c r="G64" t="s">
-        <v>351</v>
-      </c>
       <c r="H64" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="65" spans="2:8" x14ac:dyDescent="0.2">
@@ -2997,10 +2997,10 @@
         <v>165</v>
       </c>
       <c r="E65" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="F65" s="3" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="G65" t="s">
         <v>167</v>
@@ -3014,22 +3014,22 @@
         <v>169</v>
       </c>
       <c r="C66" t="s">
+        <v>337</v>
+      </c>
+      <c r="D66" t="s">
         <v>338</v>
       </c>
-      <c r="D66" t="s">
+      <c r="E66" t="s">
+        <v>278</v>
+      </c>
+      <c r="F66" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="G66" t="s">
+        <v>363</v>
+      </c>
+      <c r="H66" t="s">
         <v>339</v>
-      </c>
-      <c r="E66" t="s">
-        <v>279</v>
-      </c>
-      <c r="F66" s="3" t="s">
-        <v>334</v>
-      </c>
-      <c r="G66" t="s">
-        <v>364</v>
-      </c>
-      <c r="H66" t="s">
-        <v>340</v>
       </c>
     </row>
     <row r="67" spans="2:8" x14ac:dyDescent="0.2">
@@ -3046,7 +3046,7 @@
         <v>170</v>
       </c>
       <c r="F67" s="3" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="G67" t="s">
         <v>75</v>
@@ -3066,10 +3066,10 @@
         <v>40</v>
       </c>
       <c r="E68" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F68" s="3" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="G68" t="s">
         <v>42</v>
@@ -3092,7 +3092,7 @@
         <v>180</v>
       </c>
       <c r="F69" s="3" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="G69" t="s">
         <v>186</v>
@@ -3115,7 +3115,7 @@
         <v>183</v>
       </c>
       <c r="F70" s="3" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="G70" t="s">
         <v>187</v>
@@ -3138,7 +3138,7 @@
         <v>191</v>
       </c>
       <c r="F71" s="3" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="G71" t="s">
         <v>194</v>
@@ -3161,7 +3161,7 @@
         <v>193</v>
       </c>
       <c r="F72" s="3" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="G72" t="s">
         <v>195</v>

--- a/data/liste-equipe.xlsx
+++ b/data/liste-equipe.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10209"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10921"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jeremylavalade/Library/CloudStorage/GoogleDrive-b00730264@essec.edu/Drive partagés/L'Harmonie du Doute/3. Services Supports/3. Com' Externe (hors financement)/2. Site Web/2. Site Web/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92D1F7A4-9A68-8545-8198-7A8653D944E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2A1B341-A953-E84D-8F2F-7BF1BDDAAD54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17740" xr2:uid="{786A410D-58C9-CF4E-A296-84671034DD88}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="498" uniqueCount="365">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="498" uniqueCount="363">
   <si>
     <t>Prénom</t>
   </si>
@@ -554,9 +554,6 @@
     <t>Chef Opérateur Son</t>
   </si>
   <si>
-    <t>Régisseur Adjoint</t>
-  </si>
-  <si>
     <t>Mondésir</t>
   </si>
   <si>
@@ -924,9 +921,6 @@
   </si>
   <si>
     <t>Unit Manager</t>
-  </si>
-  <si>
-    <t>Assistant Unit Manager</t>
   </si>
   <si>
     <t>Unit</t>
@@ -1548,7 +1542,7 @@
         <v>13</v>
       </c>
       <c r="F2" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="G2" t="s">
         <v>2</v>
@@ -1557,7 +1551,7 @@
         <v>3</v>
       </c>
       <c r="J2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="3" spans="2:10" x14ac:dyDescent="0.2">
@@ -1574,7 +1568,7 @@
         <v>11</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="G3" t="s">
         <v>19</v>
@@ -1597,7 +1591,7 @@
         <v>16</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="G4" t="s">
         <v>17</v>
@@ -1620,7 +1614,7 @@
         <v>23</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>25</v>
@@ -1634,22 +1628,22 @@
         <v>27</v>
       </c>
       <c r="C6" t="s">
+        <v>183</v>
+      </c>
+      <c r="D6" t="s">
         <v>184</v>
-      </c>
-      <c r="D6" t="s">
-        <v>185</v>
       </c>
       <c r="E6" t="s">
         <v>24</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="G6" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H6" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="7" spans="2:10" x14ac:dyDescent="0.2">
@@ -1666,7 +1660,7 @@
         <v>24</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="G7" t="s">
         <v>149</v>
@@ -1686,16 +1680,16 @@
         <v>151</v>
       </c>
       <c r="E8" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="G8" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H8" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.2">
@@ -1703,22 +1697,22 @@
         <v>28</v>
       </c>
       <c r="C9" t="s">
+        <v>197</v>
+      </c>
+      <c r="D9" t="s">
         <v>198</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>199</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="G9" t="s">
         <v>200</v>
       </c>
-      <c r="F9" s="3" t="s">
-        <v>292</v>
-      </c>
-      <c r="G9" t="s">
+      <c r="H9" t="s">
         <v>201</v>
-      </c>
-      <c r="H9" t="s">
-        <v>202</v>
       </c>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.2">
@@ -1726,22 +1720,22 @@
         <v>28</v>
       </c>
       <c r="C10" t="s">
+        <v>202</v>
+      </c>
+      <c r="D10" t="s">
         <v>203</v>
       </c>
-      <c r="D10" t="s">
+      <c r="E10" t="s">
         <v>204</v>
       </c>
-      <c r="E10" t="s">
+      <c r="F10" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="G10" t="s">
         <v>205</v>
       </c>
-      <c r="F10" s="3" t="s">
-        <v>293</v>
-      </c>
-      <c r="G10" t="s">
+      <c r="H10" t="s">
         <v>206</v>
-      </c>
-      <c r="H10" t="s">
-        <v>207</v>
       </c>
     </row>
     <row r="11" spans="2:10" x14ac:dyDescent="0.2">
@@ -1758,7 +1752,7 @@
         <v>33</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="G11" t="s">
         <v>37</v>
@@ -1781,13 +1775,13 @@
         <v>36</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="G12" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H12" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="13" spans="2:10" x14ac:dyDescent="0.2">
@@ -1801,16 +1795,16 @@
         <v>154</v>
       </c>
       <c r="E13" t="s">
-        <v>172</v>
+        <v>152</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="G13" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H13" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="14" spans="2:10" x14ac:dyDescent="0.2">
@@ -1818,22 +1812,22 @@
         <v>27</v>
       </c>
       <c r="C14" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D14" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="E14" t="s">
         <v>152</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="G14" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H14" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="15" spans="2:10" x14ac:dyDescent="0.2">
@@ -1841,22 +1835,22 @@
         <v>27</v>
       </c>
       <c r="C15" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="D15" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="E15" t="s">
         <v>152</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="G15" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H15" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="16" spans="2:10" x14ac:dyDescent="0.2">
@@ -1864,22 +1858,22 @@
         <v>27</v>
       </c>
       <c r="C16" t="s">
+        <v>207</v>
+      </c>
+      <c r="D16" t="s">
         <v>208</v>
-      </c>
-      <c r="D16" t="s">
-        <v>209</v>
       </c>
       <c r="E16" t="s">
         <v>152</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="G16" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H16" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="17" spans="2:8" x14ac:dyDescent="0.2">
@@ -1887,22 +1881,22 @@
         <v>27</v>
       </c>
       <c r="C17" t="s">
+        <v>209</v>
+      </c>
+      <c r="D17" t="s">
         <v>210</v>
-      </c>
-      <c r="D17" t="s">
-        <v>211</v>
       </c>
       <c r="E17" t="s">
         <v>152</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="G17" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H17" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.2">
@@ -1919,7 +1913,7 @@
         <v>41</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="G18" t="s">
         <v>42</v>
@@ -1942,7 +1936,7 @@
         <v>157</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="G19" t="s">
         <v>158</v>
@@ -1956,22 +1950,22 @@
         <v>29</v>
       </c>
       <c r="C20" t="s">
+        <v>211</v>
+      </c>
+      <c r="D20" t="s">
         <v>212</v>
       </c>
-      <c r="D20" t="s">
+      <c r="E20" t="s">
+        <v>279</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="G20" t="s">
         <v>213</v>
       </c>
-      <c r="E20" t="s">
-        <v>280</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>300</v>
-      </c>
-      <c r="G20" t="s">
+      <c r="H20" t="s">
         <v>214</v>
-      </c>
-      <c r="H20" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.2">
@@ -1979,22 +1973,22 @@
         <v>29</v>
       </c>
       <c r="C21" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="D21" t="s">
+        <v>215</v>
+      </c>
+      <c r="E21" t="s">
         <v>216</v>
       </c>
-      <c r="E21" t="s">
+      <c r="F21" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="G21" t="s">
         <v>217</v>
       </c>
-      <c r="F21" s="3" t="s">
-        <v>301</v>
-      </c>
-      <c r="G21" t="s">
-        <v>218</v>
-      </c>
       <c r="H21" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.2">
@@ -2002,22 +1996,22 @@
         <v>29</v>
       </c>
       <c r="C22" t="s">
+        <v>218</v>
+      </c>
+      <c r="D22" t="s">
         <v>219</v>
       </c>
-      <c r="D22" t="s">
+      <c r="E22" t="s">
         <v>220</v>
       </c>
-      <c r="E22" t="s">
+      <c r="F22" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="G22" t="s">
         <v>221</v>
       </c>
-      <c r="F22" s="3" t="s">
-        <v>302</v>
-      </c>
-      <c r="G22" t="s">
+      <c r="H22" t="s">
         <v>222</v>
-      </c>
-      <c r="H22" t="s">
-        <v>223</v>
       </c>
     </row>
     <row r="23" spans="2:8" ht="17" x14ac:dyDescent="0.2">
@@ -2025,22 +2019,22 @@
         <v>29</v>
       </c>
       <c r="C23" t="s">
+        <v>223</v>
+      </c>
+      <c r="D23" t="s">
         <v>224</v>
       </c>
-      <c r="D23" t="s">
+      <c r="E23" t="s">
+        <v>220</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="H23" t="s">
         <v>225</v>
-      </c>
-      <c r="E23" t="s">
-        <v>221</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>302</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="H23" t="s">
-        <v>226</v>
       </c>
     </row>
     <row r="24" spans="2:8" x14ac:dyDescent="0.2">
@@ -2048,22 +2042,22 @@
         <v>29</v>
       </c>
       <c r="C24" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D24" t="s">
+        <v>226</v>
+      </c>
+      <c r="E24" t="s">
         <v>227</v>
       </c>
-      <c r="E24" t="s">
+      <c r="F24" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="G24" t="s">
         <v>228</v>
       </c>
-      <c r="F24" s="3" t="s">
-        <v>303</v>
-      </c>
-      <c r="G24" t="s">
+      <c r="H24" t="s">
         <v>229</v>
-      </c>
-      <c r="H24" t="s">
-        <v>230</v>
       </c>
     </row>
     <row r="25" spans="2:8" x14ac:dyDescent="0.2">
@@ -2080,7 +2074,7 @@
         <v>46</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="G25" t="s">
         <v>52</v>
@@ -2103,7 +2097,7 @@
         <v>46</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="G26" t="s">
         <v>54</v>
@@ -2126,7 +2120,7 @@
         <v>51</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="G27" t="s">
         <v>56</v>
@@ -2149,7 +2143,7 @@
         <v>161</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="G28" t="s">
         <v>162</v>
@@ -2172,13 +2166,13 @@
         <v>59</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="G29" t="s">
         <v>7</v>
       </c>
       <c r="H29" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="30" spans="2:8" x14ac:dyDescent="0.2">
@@ -2186,22 +2180,22 @@
         <v>28</v>
       </c>
       <c r="C30" t="s">
+        <v>230</v>
+      </c>
+      <c r="D30" t="s">
         <v>231</v>
       </c>
-      <c r="D30" t="s">
+      <c r="E30" t="s">
         <v>232</v>
       </c>
-      <c r="E30" t="s">
+      <c r="F30" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="G30" t="s">
         <v>233</v>
       </c>
-      <c r="F30" s="3" t="s">
-        <v>308</v>
-      </c>
-      <c r="G30" t="s">
+      <c r="H30" t="s">
         <v>234</v>
-      </c>
-      <c r="H30" t="s">
-        <v>235</v>
       </c>
     </row>
     <row r="31" spans="2:8" x14ac:dyDescent="0.2">
@@ -2209,22 +2203,22 @@
         <v>28</v>
       </c>
       <c r="C31" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D31" t="s">
+        <v>235</v>
+      </c>
+      <c r="E31" t="s">
+        <v>232</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="G31" t="s">
         <v>236</v>
       </c>
-      <c r="E31" t="s">
-        <v>233</v>
-      </c>
-      <c r="F31" s="3" t="s">
-        <v>308</v>
-      </c>
-      <c r="G31" t="s">
+      <c r="H31" t="s">
         <v>237</v>
-      </c>
-      <c r="H31" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="32" spans="2:8" x14ac:dyDescent="0.2">
@@ -2232,22 +2226,22 @@
         <v>28</v>
       </c>
       <c r="C32" t="s">
+        <v>238</v>
+      </c>
+      <c r="D32" t="s">
         <v>239</v>
       </c>
-      <c r="D32" t="s">
+      <c r="E32" t="s">
         <v>240</v>
       </c>
-      <c r="E32" t="s">
+      <c r="F32" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="G32" t="s">
         <v>241</v>
       </c>
-      <c r="F32" s="3" t="s">
-        <v>308</v>
-      </c>
-      <c r="G32" t="s">
+      <c r="H32" t="s">
         <v>242</v>
-      </c>
-      <c r="H32" t="s">
-        <v>243</v>
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.2">
@@ -2255,22 +2249,22 @@
         <v>28</v>
       </c>
       <c r="C33" t="s">
+        <v>243</v>
+      </c>
+      <c r="D33" t="s">
         <v>244</v>
       </c>
-      <c r="D33" t="s">
+      <c r="E33" t="s">
+        <v>232</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="G33" t="s">
         <v>245</v>
       </c>
-      <c r="E33" t="s">
-        <v>233</v>
-      </c>
-      <c r="F33" s="3" t="s">
-        <v>308</v>
-      </c>
-      <c r="G33" t="s">
+      <c r="H33" t="s">
         <v>246</v>
-      </c>
-      <c r="H33" t="s">
-        <v>247</v>
       </c>
     </row>
     <row r="34" spans="2:8" x14ac:dyDescent="0.2">
@@ -2278,22 +2272,22 @@
         <v>28</v>
       </c>
       <c r="C34" t="s">
+        <v>247</v>
+      </c>
+      <c r="D34" t="s">
         <v>248</v>
       </c>
-      <c r="D34" t="s">
+      <c r="E34" t="s">
+        <v>240</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="G34" t="s">
         <v>249</v>
       </c>
-      <c r="E34" t="s">
-        <v>241</v>
-      </c>
-      <c r="F34" s="3" t="s">
-        <v>308</v>
-      </c>
-      <c r="G34" t="s">
+      <c r="H34" t="s">
         <v>250</v>
-      </c>
-      <c r="H34" t="s">
-        <v>251</v>
       </c>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.2">
@@ -2301,22 +2295,22 @@
         <v>28</v>
       </c>
       <c r="C35" t="s">
+        <v>251</v>
+      </c>
+      <c r="D35" t="s">
         <v>252</v>
       </c>
-      <c r="D35" t="s">
+      <c r="E35" t="s">
         <v>253</v>
       </c>
-      <c r="E35" t="s">
+      <c r="F35" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="G35" t="s">
         <v>254</v>
       </c>
-      <c r="F35" s="3" t="s">
-        <v>309</v>
-      </c>
-      <c r="G35" t="s">
+      <c r="H35" t="s">
         <v>255</v>
-      </c>
-      <c r="H35" t="s">
-        <v>256</v>
       </c>
     </row>
     <row r="36" spans="2:8" x14ac:dyDescent="0.2">
@@ -2324,22 +2318,22 @@
         <v>28</v>
       </c>
       <c r="C36" t="s">
+        <v>256</v>
+      </c>
+      <c r="D36" t="s">
         <v>257</v>
       </c>
-      <c r="D36" t="s">
+      <c r="E36" t="s">
         <v>258</v>
       </c>
-      <c r="E36" t="s">
+      <c r="F36" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="G36" t="s">
         <v>259</v>
       </c>
-      <c r="F36" s="3" t="s">
-        <v>310</v>
-      </c>
-      <c r="G36" t="s">
+      <c r="H36" t="s">
         <v>260</v>
-      </c>
-      <c r="H36" t="s">
-        <v>261</v>
       </c>
     </row>
     <row r="37" spans="2:8" x14ac:dyDescent="0.2">
@@ -2356,7 +2350,7 @@
         <v>62</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="G37" t="s">
         <v>63</v>
@@ -2379,7 +2373,7 @@
         <v>171</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="G38" t="s">
         <v>75</v>
@@ -2402,7 +2396,7 @@
         <v>68</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="G39" t="s">
         <v>77</v>
@@ -2425,7 +2419,7 @@
         <v>71</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="G40" t="s">
         <v>79</v>
@@ -2448,7 +2442,7 @@
         <v>74</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="G41" t="s">
         <v>81</v>
@@ -2468,10 +2462,10 @@
         <v>84</v>
       </c>
       <c r="E42" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="G42" t="s">
         <v>85</v>
@@ -2485,22 +2479,22 @@
         <v>28</v>
       </c>
       <c r="C43" t="s">
+        <v>261</v>
+      </c>
+      <c r="D43" t="s">
         <v>262</v>
       </c>
-      <c r="D43" t="s">
+      <c r="E43" t="s">
+        <v>282</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="G43" t="s">
+        <v>283</v>
+      </c>
+      <c r="H43" t="s">
         <v>263</v>
-      </c>
-      <c r="E43" t="s">
-        <v>283</v>
-      </c>
-      <c r="F43" s="3" t="s">
-        <v>316</v>
-      </c>
-      <c r="G43" t="s">
-        <v>284</v>
-      </c>
-      <c r="H43" t="s">
-        <v>264</v>
       </c>
     </row>
     <row r="44" spans="2:8" x14ac:dyDescent="0.2">
@@ -2508,22 +2502,22 @@
         <v>29</v>
       </c>
       <c r="C44" t="s">
+        <v>264</v>
+      </c>
+      <c r="D44" t="s">
         <v>265</v>
       </c>
-      <c r="D44" t="s">
+      <c r="E44" t="s">
         <v>266</v>
       </c>
-      <c r="E44" t="s">
+      <c r="F44" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="G44" t="s">
         <v>267</v>
       </c>
-      <c r="F44" s="3" t="s">
-        <v>317</v>
-      </c>
-      <c r="G44" t="s">
+      <c r="H44" t="s">
         <v>268</v>
-      </c>
-      <c r="H44" t="s">
-        <v>269</v>
       </c>
     </row>
     <row r="45" spans="2:8" x14ac:dyDescent="0.2">
@@ -2531,22 +2525,22 @@
         <v>29</v>
       </c>
       <c r="C45" t="s">
+        <v>269</v>
+      </c>
+      <c r="D45" t="s">
         <v>270</v>
       </c>
-      <c r="D45" t="s">
+      <c r="E45" t="s">
         <v>271</v>
       </c>
-      <c r="E45" t="s">
+      <c r="F45" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="G45" t="s">
         <v>272</v>
       </c>
-      <c r="F45" s="3" t="s">
-        <v>318</v>
-      </c>
-      <c r="G45" t="s">
+      <c r="H45" t="s">
         <v>273</v>
-      </c>
-      <c r="H45" t="s">
-        <v>274</v>
       </c>
     </row>
     <row r="46" spans="2:8" x14ac:dyDescent="0.2">
@@ -2554,22 +2548,22 @@
         <v>29</v>
       </c>
       <c r="C46" t="s">
+        <v>356</v>
+      </c>
+      <c r="D46" t="s">
+        <v>357</v>
+      </c>
+      <c r="E46" t="s">
         <v>358</v>
       </c>
-      <c r="D46" t="s">
+      <c r="F46" s="3" t="s">
         <v>359</v>
       </c>
-      <c r="E46" t="s">
+      <c r="G46" t="s">
         <v>360</v>
       </c>
-      <c r="F46" s="3" t="s">
-        <v>361</v>
-      </c>
-      <c r="G46" t="s">
-        <v>362</v>
-      </c>
       <c r="H46" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="47" spans="2:8" x14ac:dyDescent="0.2">
@@ -2586,7 +2580,7 @@
         <v>166</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="G47" t="s">
         <v>167</v>
@@ -2603,19 +2597,19 @@
         <v>94</v>
       </c>
       <c r="D48" t="s">
+        <v>274</v>
+      </c>
+      <c r="E48" t="s">
         <v>275</v>
       </c>
-      <c r="E48" t="s">
+      <c r="F48" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="G48" t="s">
+        <v>284</v>
+      </c>
+      <c r="H48" t="s">
         <v>276</v>
-      </c>
-      <c r="F48" s="3" t="s">
-        <v>320</v>
-      </c>
-      <c r="G48" t="s">
-        <v>285</v>
-      </c>
-      <c r="H48" t="s">
-        <v>277</v>
       </c>
     </row>
     <row r="49" spans="2:8" x14ac:dyDescent="0.2">
@@ -2623,22 +2617,22 @@
         <v>28</v>
       </c>
       <c r="C49" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="D49" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="E49" t="s">
         <v>87</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="G49" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H49" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
     </row>
     <row r="50" spans="2:8" x14ac:dyDescent="0.2">
@@ -2649,19 +2643,19 @@
         <v>140</v>
       </c>
       <c r="D50" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E50" t="s">
         <v>141</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="G50" t="s">
+        <v>173</v>
+      </c>
+      <c r="H50" t="s">
         <v>174</v>
-      </c>
-      <c r="H50" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="51" spans="2:8" x14ac:dyDescent="0.2">
@@ -2678,7 +2672,7 @@
         <v>141</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="G51" t="s">
         <v>63</v>
@@ -2701,7 +2695,7 @@
         <v>104</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="G52" t="s">
         <v>127</v>
@@ -2724,7 +2718,7 @@
         <v>93</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="G53" t="s">
         <v>119</v>
@@ -2744,10 +2738,10 @@
         <v>89</v>
       </c>
       <c r="E54" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="G54" t="s">
         <v>5</v>
@@ -2770,7 +2764,7 @@
         <v>96</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="G55" t="s">
         <v>121</v>
@@ -2793,7 +2787,7 @@
         <v>99</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="G56" t="s">
         <v>123</v>
@@ -2816,7 +2810,7 @@
         <v>102</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="G57" t="s">
         <v>125</v>
@@ -2839,7 +2833,7 @@
         <v>107</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="G58" t="s">
         <v>129</v>
@@ -2862,7 +2856,7 @@
         <v>110</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="G59" t="s">
         <v>131</v>
@@ -2931,7 +2925,7 @@
         <v>118</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="G62" t="s">
         <v>137</v>
@@ -2954,7 +2948,7 @@
         <v>144</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="G63" t="s">
         <v>145</v>
@@ -2968,22 +2962,22 @@
         <v>30</v>
       </c>
       <c r="C64" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="D64" t="s">
         <v>89</v>
       </c>
       <c r="E64" t="s">
+        <v>347</v>
+      </c>
+      <c r="F64" s="3" t="s">
         <v>349</v>
       </c>
-      <c r="F64" s="3" t="s">
-        <v>351</v>
-      </c>
       <c r="G64" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="H64" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
     </row>
     <row r="65" spans="2:8" x14ac:dyDescent="0.2">
@@ -2997,10 +2991,10 @@
         <v>165</v>
       </c>
       <c r="E65" t="s">
+        <v>350</v>
+      </c>
+      <c r="F65" s="3" t="s">
         <v>352</v>
-      </c>
-      <c r="F65" s="3" t="s">
-        <v>354</v>
       </c>
       <c r="G65" t="s">
         <v>167</v>
@@ -3014,22 +3008,22 @@
         <v>169</v>
       </c>
       <c r="C66" t="s">
+        <v>335</v>
+      </c>
+      <c r="D66" t="s">
+        <v>336</v>
+      </c>
+      <c r="E66" t="s">
+        <v>277</v>
+      </c>
+      <c r="F66" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="G66" t="s">
+        <v>361</v>
+      </c>
+      <c r="H66" t="s">
         <v>337</v>
-      </c>
-      <c r="D66" t="s">
-        <v>338</v>
-      </c>
-      <c r="E66" t="s">
-        <v>278</v>
-      </c>
-      <c r="F66" s="3" t="s">
-        <v>333</v>
-      </c>
-      <c r="G66" t="s">
-        <v>363</v>
-      </c>
-      <c r="H66" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="67" spans="2:8" x14ac:dyDescent="0.2">
@@ -3046,7 +3040,7 @@
         <v>170</v>
       </c>
       <c r="F67" s="3" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="G67" t="s">
         <v>75</v>
@@ -3066,10 +3060,10 @@
         <v>40</v>
       </c>
       <c r="E68" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="F68" s="3" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="G68" t="s">
         <v>42</v>
@@ -3080,94 +3074,94 @@
     </row>
     <row r="69" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B69" t="s">
+        <v>176</v>
+      </c>
+      <c r="C69" t="s">
         <v>177</v>
       </c>
-      <c r="C69" t="s">
+      <c r="D69" t="s">
         <v>178</v>
       </c>
-      <c r="D69" t="s">
+      <c r="E69" t="s">
         <v>179</v>
       </c>
-      <c r="E69" t="s">
-        <v>180</v>
-      </c>
       <c r="F69" s="3" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="G69" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H69" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="70" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B70" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C70" t="s">
+        <v>180</v>
+      </c>
+      <c r="D70" t="s">
         <v>181</v>
       </c>
-      <c r="D70" t="s">
+      <c r="E70" t="s">
         <v>182</v>
       </c>
-      <c r="E70" t="s">
-        <v>183</v>
-      </c>
       <c r="F70" s="3" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="G70" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="H70" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="71" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B71" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C71" t="s">
+        <v>188</v>
+      </c>
+      <c r="D71" t="s">
         <v>189</v>
       </c>
-      <c r="D71" t="s">
+      <c r="E71" t="s">
         <v>190</v>
       </c>
-      <c r="E71" t="s">
-        <v>191</v>
-      </c>
       <c r="F71" s="3" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="G71" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H71" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="72" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B72" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C72" t="s">
         <v>155</v>
       </c>
       <c r="D72" t="s">
+        <v>191</v>
+      </c>
+      <c r="E72" t="s">
         <v>192</v>
       </c>
-      <c r="E72" t="s">
-        <v>193</v>
-      </c>
       <c r="F72" s="3" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="G72" t="s">
+        <v>194</v>
+      </c>
+      <c r="H72" t="s">
         <v>195</v>
-      </c>
-      <c r="H72" t="s">
-        <v>196</v>
       </c>
     </row>
   </sheetData>
